--- a/bom/smart_pouch_technical_reference.xlsx
+++ b/bom/smart_pouch_technical_reference.xlsx
@@ -471,10 +471,10 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -486,7 +486,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,14 +612,40 @@
           <t>C307331</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>CL05B104KB54PNC</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>8473497</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M2" s="2" t="n">
         <v>2</v>
       </c>
@@ -632,14 +658,22 @@
       <c r="P2" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>100 nF 0402 X7R 50 V; chosen over 16 V parts for rail-margin safety.</t>
-        </is>
-      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>0.1976</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>0.1976</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -662,14 +696,40 @@
           <t>C52923</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>CL05A105KA5NQNC</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1uF 25V X5R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>3736735</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M3" s="2" t="n">
         <v>2</v>
       </c>
@@ -682,14 +742,22 @@
       <c r="P3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>1 uF 0402 X5R 25 V.</t>
-        </is>
-      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0.0142</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>0.1420</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>0.1420</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -712,14 +780,40 @@
           <t>C15850</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>CL21A106KAYNNNE</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>3352704</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="M4" s="2" t="n">
         <v>2</v>
       </c>
@@ -732,14 +826,22 @@
       <c r="P4" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>10 uF 0805 X5R 25 V.</t>
-        </is>
-      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0.0643</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>0.9002</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0.9002</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -762,14 +864,40 @@
           <t>C52306</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CL32A226KAJNNNE</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22uF 25V X5R ±10% 1210 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>207316</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M5" s="2" t="n">
         <v>2</v>
       </c>
@@ -782,14 +910,22 @@
       <c r="P5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>22 uF 1210 X5R 25 V.</t>
-        </is>
-      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.1814</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>0.7256</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0.7256</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -812,14 +948,40 @@
           <t>C778333</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>EYANG(Shenzhen Eyang Tech Development)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>C0402C0G0R6B500NTB</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0.6pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M6" s="2" t="n">
         <v>2</v>
       </c>
@@ -832,14 +994,22 @@
       <c r="P6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>RF antenna matching capacitor. Original schematic said 0.5uF, but this is the nRF52840 antenna match; using stocked 0.6pF 0402 C0G.</t>
-        </is>
-      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.0029</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>0.0058</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0.0058</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -862,14 +1032,40 @@
           <t>C3875120</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Venkel</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>C0402C0G500-0R8BNP</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0.8pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>9750</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M7" s="2" t="n">
         <v>2</v>
       </c>
@@ -882,14 +1078,22 @@
       <c r="P7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>RF antenna matching capacitor. Original schematic said 0.8uF, but this is the nRF52840 antenna match; using 0.8pF 0402 C0G.</t>
-        </is>
-      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.0105</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>0.0210</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0.0210</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -912,14 +1116,40 @@
           <t>C1547</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>FH (Guangdong Fenghua Advanced Tech)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0402CG120J500NT</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12pF 50V C0G ±5% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1098414</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M8" s="2" t="n">
         <v>2</v>
       </c>
@@ -932,14 +1162,22 @@
       <c r="P8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>12 pF 0402 C0G/NP0 50 V.</t>
-        </is>
-      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>0.0144</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0.0144</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -962,14 +1200,40 @@
           <t>C160352</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>B2B-PH-SM4-TB(LF)(SN)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 100V 1x2P 2 2A 2P 2mm 6.6mm 7.95mm 7mm Auxiliary Solder Pin Beige Copper alloy PA PH Surface Mount,Vertical Tin UL94V-0 SMD,P=2mm Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=2mm</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M9" s="2" t="n">
         <v>2</v>
       </c>
@@ -982,14 +1246,22 @@
       <c r="P9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>SMD JST PH 2-pin battery connector replacing through-hole B2B-PH-K-S.</t>
-        </is>
-      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.3586</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>0.7172</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0.7172</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1012,14 +1284,40 @@
           <t>C2843891</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>XINGLIGHT</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>XL-3030UWC-1W-3V</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 120° 1W 3.4V 350mA 6500K~7000K Discrete Diode Top-mount White Yellow Lens SMD3030-2P LED Indication - Discrete ROHS</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>SMD3030-2P</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>167844</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="M10" s="2" t="n">
         <v>2</v>
       </c>
@@ -1032,14 +1330,22 @@
       <c r="P10" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>White 3030 LED; verify current/thermal target.</t>
-        </is>
-      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1062,14 +1368,40 @@
           <t>C151304</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Littelfuse</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SP3012-04UTG</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+125℃ 0.5pF 1.5uA 4A@8/20us 5V 8.4V ESD Four channels IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 UDFN-10(1x2.5) ESD and Surge Protection (TVS/ESD) ROHS</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>UDFN-10(1x2.5)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>5164</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M11" s="2" t="n">
         <v>2</v>
       </c>
@@ -1082,14 +1414,22 @@
       <c r="P11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>SP3012-04UTG SIM ESD protection array.</t>
-        </is>
-      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.2974</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>0.5948</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0.5948</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1112,14 +1452,40 @@
           <t>C2827688</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>TECH PUBLIC</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>PRTR5V0U2X</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+125℃ 0.3pF、0.8pF 100W 10V、15V 5V 6.5V 6A 80nA ESD IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 Three channels Unidirectional SOT-143 ESD and Surge Protection (TVS/ESD) ROHS</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>SOT-143</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>60459</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M12" s="2" t="n">
         <v>2</v>
       </c>
@@ -1132,14 +1498,22 @@
       <c r="P12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>PRTR5V0U2X USB ESD.</t>
-        </is>
-      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.0609</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>0.1218</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0.1218</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1162,14 +1536,40 @@
           <t>C8678</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>MDD(Microdiode Semiconductor)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SS34</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+125℃ 3A 40V 500uA@40V 550mV@3A Independent SMA(DO-214AC) Schottky Diodes ROHS</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>SMA(DO-214AC)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>3735309</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="M13" s="2" t="n">
         <v>2</v>
       </c>
@@ -1182,14 +1582,22 @@
       <c r="P13" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>SS34 40V 3A Schottky diode SMA.</t>
-        </is>
-      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.0301</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>0.1806</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0.1806</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1212,14 +1620,40 @@
           <t>C146125</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>BOOMELE(Boom Precision Elec)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>XH-2PVertical welding</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 12mm 1x2P 2 2.5mm 250V 2P 3A 6mm 7.8mm Beige LCP Phosphor bronze Surface Mount,Vertical Tin UL94V-0 XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=2.5mm</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>11017</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>57</v>
+      </c>
       <c r="M14" s="2" t="n">
         <v>2</v>
       </c>
@@ -1232,14 +1666,22 @@
       <c r="P14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>SMD 2-pin XH-style connector for +12 V siren/load output; intentionally different from battery PH connector.</t>
-        </is>
-      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.0669</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>0.1338</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0.1338</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1262,14 +1704,40 @@
           <t>C2681544</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>SHOU HAN</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2.54-3P LT</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1x3P 2.5mm 250V 3 3A 3P Beige Brass LCP Surface Mount,Vertical Tin UL94V-0 XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=2.5mm</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1331</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>500</v>
+      </c>
       <c r="M15" s="2" t="n">
         <v>2</v>
       </c>
@@ -1282,14 +1750,22 @@
       <c r="P15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>SMD 3-pin 2.54 mm connector selected for the trimmer/control path.</t>
-        </is>
-      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.0814</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>0.1628</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>0.1628</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1312,14 +1788,40 @@
           <t>C266888</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>XUNPU</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>SMN-303</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1.37mm Connector and Ejector Nano-SIM Card Push-Push With Card Detect SMD SIM Card Connectors ROHS</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>119092</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="M16" s="2" t="n">
         <v>2</v>
       </c>
@@ -1332,14 +1834,22 @@
       <c r="P16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>SIM card connector SMN-303.</t>
-        </is>
-      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.4894</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>0.9788</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0.9788</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1362,14 +1872,40 @@
           <t>C2849472</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>DMBJ</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>PNLS4030-100M 10UH</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10uH 120mΩ 2A 2A Magnetic Shielded Inductor ±20% SMD,4x4mm Power Inductors ROHS</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>SMD,4x4mm</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>10402</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="M17" s="2" t="n">
         <v>2</v>
       </c>
@@ -1382,14 +1918,22 @@
       <c r="P17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>10 uH shielded power inductor, 4x4 mm class.</t>
-        </is>
-      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.0521</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>0.2084</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0.2084</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1412,14 +1956,40 @@
           <t>C92959</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Taiyo Yuden</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>NRS4018T2R2MDGJ</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2.2A 2.2uH 3A 42mΩ ±20% SMD,4x4mm Power Inductors ROHS</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>SMD,4x4mm</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>12164</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>3500</v>
+      </c>
       <c r="M18" s="2" t="n">
         <v>2</v>
       </c>
@@ -1432,14 +2002,22 @@
       <c r="P18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2.2 uH shielded power inductor, 4x4 mm class.</t>
-        </is>
-      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0.0886</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>0.3544</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0.3544</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1462,14 +2040,40 @@
           <t>C86065</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Murata Electronics</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>LQG15HS4N7S02D</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>160mΩ 4.7nH 6GHz 700mA 8@100MHz Multilayer inductor 0402 Inductors (SMD) ROHS</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>370072</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M19" s="2" t="n">
         <v>2</v>
       </c>
@@ -1482,14 +2086,22 @@
       <c r="P19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4.7 nH RF matching inductor; schematic footprint should be 0402, not the 4x4 power inductor footprint.</t>
-        </is>
-      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1512,14 +2124,40 @@
           <t>C60105</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Everlight Elec</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19-237/R6GHBHC-A01/2T</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>120° Common Anode SMD-4P,1.6x1.6mm RGB LEDs ROHS</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>SMD-4P,1.6x1.6mm</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>52185</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="M20" s="2" t="n">
         <v>2</v>
       </c>
@@ -1532,14 +2170,22 @@
       <c r="P20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>19-237/R6GHBHC-A01/2T bicolor red/green status LED.</t>
-        </is>
-      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.0624</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>0.2496</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0.2496</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1562,14 +2208,40 @@
           <t>C456012</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>SHOU HAN</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>TYPE-C 6P</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 1 3,000 Cycles 3A 5V 6P Black Female Surface Mount, Right Angle Type-C SMD USB Connectors ROHS</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>585486</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M21" s="2" t="n">
         <v>2</v>
       </c>
@@ -1582,14 +2254,22 @@
       <c r="P21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>USB-C 6-pin receptacle.</t>
-        </is>
-      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.0385</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>0.0770</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>0.0770</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1612,14 +2292,40 @@
           <t>C3018484</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>FUXINSEMI</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>BSS84</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+150℃ 1 P-Channel 10pF 10Ω@5V 130mA 225mW 2V 30pF 50V 5pF SOT-23 MOSFETs ROHS</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>18156</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M22" s="2" t="n">
         <v>2</v>
       </c>
@@ -1632,14 +2338,22 @@
       <c r="P22" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>BSS84 P-channel MOSFET.</t>
-        </is>
-      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.0223</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0.1338</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0.1338</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1662,14 +2376,40 @@
           <t>C8545</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Jiangsu Changjing Electronics Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2N7002</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1 N-channel 115mA 2.5V 225mW 50pF 5pF 5Ω@10V 60V SOT-23 MOSFETs ROHS</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>509621</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M23" s="2" t="n">
         <v>2</v>
       </c>
@@ -1682,14 +2422,22 @@
       <c r="P23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2N7002 N-channel MOSFET.</t>
-        </is>
-      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.0154</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>0.0924</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0.0924</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1712,14 +2460,40 @@
           <t>C25792</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF4702TCE</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 47kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1476306</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M24" s="2" t="n">
         <v>2</v>
       </c>
@@ -1732,14 +2506,22 @@
       <c r="P24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>47 kOhm 0402 1%.</t>
-        </is>
-      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1762,14 +2544,40 @@
           <t>C22369540</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>HKR(Hong Kong Resistors)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>RCA02150KFLF</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 150kΩ 50V 62.5mW Thick Film Resistor ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>517</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M25" s="2" t="n">
         <v>2</v>
       </c>
@@ -1782,14 +2590,22 @@
       <c r="P25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr"/>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>150 kOhm 0402 1%.</t>
-        </is>
-      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>0.0008</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0.0008</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1812,14 +2628,40 @@
           <t>C49330233</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>HKR(Hong Kong Resistors)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>AS0210KF</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 10kΩ 50V 62.5mW ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1820</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M26" s="2" t="n">
         <v>2</v>
       </c>
@@ -1832,14 +2674,22 @@
       <c r="P26" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>10 kOhm 0402 1%; min-1 alternative to Basic C25744.</t>
-        </is>
-      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.0016</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>0.0128</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0.0128</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1862,14 +2712,40 @@
           <t>C25104</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF3300TCE</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 330Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>918201</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M27" s="2" t="n">
         <v>2</v>
       </c>
@@ -1882,14 +2758,22 @@
       <c r="P27" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr"/>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>330 Ohm 0402 1%; schematic footprint was blank.</t>
-        </is>
-      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1912,14 +2796,40 @@
           <t>C25169</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0402WGJ047JTCE</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 4.7Ω 50V 62.5mW Thick Film Resistor ±200ppm/℃ ±5% 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1975</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M28" s="2" t="n">
         <v>2</v>
       </c>
@@ -1932,14 +2842,22 @@
       <c r="P28" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>4.7 Ohm 0402 5%; verify tolerance is acceptable.</t>
-        </is>
-      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.0016</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>0.0256</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>0.0256</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1962,14 +2880,40 @@
           <t>C25905</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF5101TCE</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 5.1kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>2475295</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M29" s="2" t="n">
         <v>2</v>
       </c>
@@ -1982,14 +2926,22 @@
       <c r="P29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr"/>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>5.1 kOhm 0402 1%.</t>
-        </is>
-      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2012,14 +2964,40 @@
           <t>C100318</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>LIZ Elec</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>CR0402FF22R0G</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+125℃ 22Ω 50V 62.5mW Thick Film Resistor ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1744</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M30" s="2" t="n">
         <v>2</v>
       </c>
@@ -2032,14 +3010,22 @@
       <c r="P30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>22 Ohm 0402 1%.</t>
-        </is>
-      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.0006</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2062,14 +3048,40 @@
           <t>C25076</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF1000TCE</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 100Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>3450166</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M31" s="2" t="n">
         <v>2</v>
       </c>
@@ -2082,14 +3094,22 @@
       <c r="P31" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>100 Ohm 0402 1%.</t>
-        </is>
-      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2112,14 +3132,40 @@
           <t>C159084</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>RALEC</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>RTT021913FTH</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 191kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>9213</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M32" s="2" t="n">
         <v>2</v>
       </c>
@@ -2132,14 +3178,22 @@
       <c r="P32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>191 kOhm 0402 1%.</t>
-        </is>
-      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>0.0014</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0.0014</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2162,14 +3216,40 @@
           <t>C64043</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF2403TCE</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 240kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>5763</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M33" s="2" t="n">
         <v>2</v>
       </c>
@@ -2182,14 +3262,22 @@
       <c r="P33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>240 kOhm 0402 1%.</t>
-        </is>
-      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2212,14 +3300,40 @@
           <t>C144809</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>AC0402FR-07100KL</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 100kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>10265</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M34" s="2" t="n">
         <v>2</v>
       </c>
@@ -2232,14 +3346,22 @@
       <c r="P34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>100 kOhm 0402 1%; min-1 alternative to Basic C25741.</t>
-        </is>
-      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2262,14 +3384,40 @@
           <t>C25900</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF4701TCE</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 4.7kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>4025673</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M35" s="2" t="n">
         <v>2</v>
       </c>
@@ -2282,14 +3430,22 @@
       <c r="P35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>4.7 kOhm 0402 1%.</t>
-        </is>
-      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>0.0044</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>0.0044</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2312,14 +3468,40 @@
           <t>C719176</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>BOURNS</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>TC33X-2-103E</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1 10kΩ 150mW ±25% ±250ppm/℃ SMD-3P,3.8x3.6mm Potentiometers, Variable Resistors ROHS</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>SMD-3P,3.8x3.6mm</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>73160</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>2500</v>
+      </c>
       <c r="M36" s="2" t="n">
         <v>2</v>
       </c>
@@ -2332,14 +3514,22 @@
       <c r="P36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>10 kOhm SMD trimmer selected; schematic/spec did not define a previous resistance value.</t>
-        </is>
-      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0.1065</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>0.2130</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>0.2130</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2362,14 +3552,40 @@
           <t>C139797</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>ALPSALPINE</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>SKRPACE010</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>-30℃~+85℃ 16V 2.5mm 2.6N 3.2mm 4.2mm 50,000 cycles 50mA J-Lead Oval button SPST-NO Surface Mount,Vertical SMD-4P,4.2x3.2mm Tactile Switches ROHS</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>SMD-4P,4.2x3.2mm</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>129256</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>4000</v>
+      </c>
       <c r="M37" s="2" t="n">
         <v>2</v>
       </c>
@@ -2382,14 +3598,22 @@
       <c r="P37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>SMD tactile switch imported with easyeda2kicad.</t>
-        </is>
-      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.0629</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>0.1258</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>0.1258</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2412,14 +3636,40 @@
           <t>C77131</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Murata Electronics</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>NCP15XH103F03RC</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+125℃ 0.5mm 100mW 10kΩ 1mW/℃ 1mm 310uA 3380K 3434K 3455K ±1% ±1% 0402 NTC Thermistors ROHS</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>149938</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M38" s="2" t="n">
         <v>2</v>
       </c>
@@ -2432,14 +3682,22 @@
       <c r="P38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
-      <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>10 kOhm 0402 NTC thermistor.</t>
-        </is>
-      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.0199</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>0.0398</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0.0398</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2462,14 +3720,40 @@
           <t>C190794</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>NRF52840-QIAA-R</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>-95dBm 1.7V~5.5V 2.4GHz 2.4GHz~2.4835GHz 2Mbps 4.82mA 6.26mA 8dBm SPI、USB、UART、ADC、I2S、PWM ZigBee、Bluetooth、LoRa、ISM transceiver AQFN-73-EP(7x7) RF Transceiver ICs ROHS</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>AQFN-73-EP(7x7)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>31360</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M39" s="2" t="n">
         <v>2</v>
       </c>
@@ -2482,14 +3766,22 @@
       <c r="P39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>nRF52840-QIAA-R.</t>
-        </is>
-      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>5.7384</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>11.4768</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>11.4768</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2512,14 +3804,40 @@
           <t>C22397843</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>nRF9151-LACA-R7</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>LGA-113(12.1x11.1) RF Modules ROHS</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>LGA-113(12.1x11.1)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>523</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="M40" s="2" t="n">
         <v>2</v>
       </c>
@@ -2532,14 +3850,22 @@
       <c r="P40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>nRF9151-LACA-R7 selected.</t>
-        </is>
-      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>16.1428</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>32.2856</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>32.2856</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2562,14 +3888,40 @@
           <t>C25346894</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>NPM1300-CAAA-R7</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>WLCSP-35(2.4x3.1) Power Management - Specialized ROHS</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>WLCSP-35(2.4x3.1)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="M41" s="2" t="n">
         <v>2</v>
       </c>
@@ -2582,14 +3934,22 @@
       <c r="P41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>nPM1300-CAAA-R7 PMIC.</t>
-        </is>
-      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>2.5632</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>5.1264</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>5.1264</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2612,14 +3972,40 @@
           <t>C437655</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Bosch Sensortec</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>BMA400</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 1.71V~3.6V 12bit 160nA 1KB Accelerometer SPI、I2C X,Y,Z ±16g LGA-12(2x2) Accelerometers ROHS</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>LGA-12(2x2)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>5405</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M42" s="2" t="n">
         <v>2</v>
       </c>
@@ -2632,14 +4018,22 @@
       <c r="P42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>BMA400 accelerometer LGA-12.</t>
-        </is>
-      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2.3952</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>4.7904</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>4.7904</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2662,14 +4056,40 @@
           <t>C5137195</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>BAT WIRELESS</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>BWU.FL-IPEX1</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1 1.25mm 2mm 50Ω 6GHz Board Side IPEX Male Pin SMD Coaxial Connectors (RF) ROHS</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>711347</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="M43" s="2" t="n">
         <v>2</v>
       </c>
@@ -2682,14 +4102,22 @@
       <c r="P43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>u.FL / IPEX1 SMD RF connector.</t>
-        </is>
-      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.0398</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>0.1592</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>0.1592</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2712,14 +4140,40 @@
           <t>C239238</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Rainsun microwave Tech</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>AN6520-245</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 0.5dBi 1mm 2 2.2mm 2.45GHz 200MHz 3W 50Ω 6.5mm SMD Antennas ROHS</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="M44" s="2" t="n">
         <v>2</v>
       </c>
@@ -2732,14 +4186,22 @@
       <c r="P44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>AN6520-245 2.4/5 GHz antenna.</t>
-        </is>
-      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0.5734</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>1.1468</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>1.1468</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2762,14 +4224,40 @@
           <t>C160405</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>SM06B-SRSS-TB(LF)(SN)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1A 1mm 1x6P 2.9mm 4.32mm 50V 6 6P 8mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>65536</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M45" s="2" t="n">
         <v>2</v>
       </c>
@@ -2782,14 +4270,22 @@
       <c r="P45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>SM06B-SRSS-TB JST SH 1.0 mm 6-pin biometric connector.</t>
-        </is>
-      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.2998</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>0.5996</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>0.5996</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2812,14 +4308,40 @@
           <t>C160404</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>SM04B-SRSS-TB(LF)(SN)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1A 1mm 1x4P 2.9mm 4 4.32mm 4P 50V 6mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>10042</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M46" s="2" t="n">
         <v>2</v>
       </c>
@@ -2832,14 +4354,22 @@
       <c r="P46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>SMD JST-SH 1.0 mm 4-pin UART connector.</t>
-        </is>
-      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.2245</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>0.4490</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>0.4490</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2862,14 +4392,40 @@
           <t>C41376037</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>hanxia</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>HX PZ1.27-2x5P TP</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+105℃ 1.27mm 1.27mm 10P 1A 1mm 2 2x5P 4mm 500V Black Brass Gold Pin Header Surface Mount,Vertical SMD,P=1.27mm Pin Headers ROHS</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=1.27mm</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>14553</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M47" s="2" t="n">
         <v>2</v>
       </c>
@@ -2882,14 +4438,22 @@
       <c r="P47" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="2" t="inlineStr"/>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>SMD 2x5 1.27 mm SWD header replacing through-hole header.</t>
-        </is>
-      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.096</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>0.384</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>0.384</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2912,14 +4476,40 @@
           <t>C84817</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>XI'AN Aerosemi Tech</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>MT3608</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 1 1.2MHz 100uA、1.6mA 2A 2V~24V Adjustable Boost Boost Built-in No SOT-23-6 DC-DC Converters ROHS</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23-6</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>182531</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M48" s="2" t="n">
         <v>2</v>
       </c>
@@ -2932,14 +4522,22 @@
       <c r="P48" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr"/>
-      <c r="S48" s="2" t="inlineStr"/>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>MT3608 boost converter SOT-23-6.</t>
-        </is>
-      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2962,14 +4560,40 @@
           <t>C187794</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Seiko Epson</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Q22FA12800025</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>-20℃~+75℃ 32MHz 60Ω 8pF Crystal Oscillator ±10ppm ±10ppm SMD2016-4P Crystals ROHS</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>SMD2016-4P</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>14435</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M49" s="2" t="n">
         <v>2</v>
       </c>
@@ -2982,14 +4606,22 @@
       <c r="P49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr"/>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>32 MHz 2016 crystal, 8 pF load; verify against final nRF52840 load-cap calculation.</t>
-        </is>
-      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.2321</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>0.4642</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>0.4642</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T49"/>

--- a/bom/smart_pouch_technical_reference.xlsx
+++ b/bom/smart_pouch_technical_reference.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reference'!$A$1:$T$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reference'!$A$1:$T$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -147,8 +147,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReferenceTable" displayName="ReferenceTable" ref="A1:T49" headerRowCount="1">
-  <autoFilter ref="A1:T49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReferenceTable" displayName="ReferenceTable" ref="A1:T63" headerRowCount="1">
+  <autoFilter ref="A1:T63"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Designators"/>
     <tableColumn id="2" name="Value"/>
@@ -464,10 +464,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -486,7 +486,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="35" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -594,7 +594,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C1,C4,C6,C8,C12,C13,C14,C15,C29,C30,C31,C32,C33</t>
+          <t>C1,C6,C8,C29,C30,C31,C32</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8473497</v>
+        <v>8002097</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1</v>
@@ -650,13 +650,13 @@
         <v>2</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -665,12 +665,12 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>0.1976</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>0.1976</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr"/>
@@ -678,7 +678,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>C2,C3,C5,C11,C24</t>
+          <t>C2,C5,C24</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3736735</v>
+        <v>3365443</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>1</v>
@@ -734,13 +734,13 @@
         <v>2</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>0.1420</t>
+          <t>0.0852</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>0.1420</t>
+          <t>0.0852</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr"/>
@@ -762,142 +762,64 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C7,C16,C18,C20,C21,C22,C23</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10uF</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Capacitor_SMD:C_0805_2012Metric</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>C15850</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>CL21A106KAYNNNE</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>3352704</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>1nF</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0.0643</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0.9002</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0.9002</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>C17,C19</t>
+          <t>C4,C34</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>22u 25V</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Capacitor_SMD:C_1210_3225Metric</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C52306</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>CL32A226KAJNNNE</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>22uF 25V X5R ±10% 1210 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1210</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>207316</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>1000</v>
-      </c>
+          <t>12pF</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="n">
         <v>2</v>
       </c>
@@ -907,106 +829,96 @@
       <c r="O5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0.1814</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0.7256</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0.7256</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C7,C16,C18,C20,C21,C22,C23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0.6pF</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_0402_1005Metric</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>C778333</t>
+          <t>C15850</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>EYANG(Shenzhen Eyang Tech Development)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>C0402C0G0R6B500NTB</t>
+          <t>CL21A106KAYNNNE</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0.6pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+          <t>10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>250</v>
+        <v>3203459</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0767</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>0.0058</t>
+          <t>1.0738</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0.0058</t>
+          <t>1.0738</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr"/>
@@ -1014,83 +926,83 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C9,C28</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0.8pF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_0402_1005Metric</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>C3875120</t>
+          <t>C15850</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Venkel</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>C0402C0G500-0R8BNP</t>
+          <t>CL21A106KAYNNNE</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0.8pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+          <t>10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9750</v>
+        <v>3203459</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0.0105</t>
+          <t>0.0767</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>0.0210</t>
+          <t>0.3068</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0.0210</t>
+          <t>0.3068</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr"/>
@@ -1098,12 +1010,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C27,C35</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>12pF</t>
+          <t>2.2uF</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1113,22 +1025,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>C1547</t>
+          <t>C307331</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>FH (Guangdong Fenghua Advanced Tech)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0402CG120J500NT</t>
+          <t>CL05B104KB54PNC</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12pF 50V C0G ±5% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1142,7 +1054,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1098414</v>
+        <v>8002097</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>1</v>
@@ -1154,27 +1066,27 @@
         <v>2</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0076</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0152</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr"/>
@@ -1182,57 +1094,57 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CN1</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>B2B-PH-SM4-TB</t>
+          <t>100pF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_B2B-PH-SM4-TB-LF-SN</t>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>C160352</t>
+          <t>C52923</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>B2B-PH-SM4-TB(LF)(SN)</t>
+          <t>CL05A105KA5NQNC</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25℃~+85℃ 1 100V 1x2P 2 2A 2P 2mm 6.6mm 7.95mm 7mm Auxiliary Solder Pin Beige Copper alloy PA PH Surface Mount,Vertical Tin UL94V-0 SMD,P=2mm Wire To Board Connector ROHS</t>
+          <t>1uF 25V X5R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SMD,P=2mm</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1007</v>
+        <v>3365443</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>2</v>
@@ -1248,17 +1160,17 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.0142</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>0.7172</t>
+          <t>0.0284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0.7172</t>
+          <t>0.0284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr"/>
@@ -1266,83 +1178,83 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>D1,D6,D7,D8,D9,D10,D11,D12</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:LED-SMD_L3.0-W3.0_XL-3030UWC-1W-3V</t>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>C2843891</t>
+          <t>C307331</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>XINGLIGHT</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>XL-3030UWC-1W-3V</t>
+          <t>CL05B104KB54PNC</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-40℃~+85℃ 120° 1W 3.4V 350mA 6500K~7000K Discrete Diode Top-mount White Yellow Lens SMD3030-2P LED Indication - Discrete ROHS</t>
+          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SMD3030-2P</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>167844</v>
+        <v>8002097</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.0076</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.0152</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.0152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr"/>
@@ -1350,58 +1262,24 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SP3012-04UTG</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>easyeda2kicad:UDFN-10_L2.5-W1.0-P0.50-BL</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>C151304</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Littelfuse</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>SP3012-04UTG</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+125℃ 0.5pF 1.5uA 4A@8/20us 5V 8.4V ESD Four channels IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 UDFN-10(1x2.5) ESD and Surge Protection (TVS/ESD) ROHS</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>UDFN-10(1x2.5)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>5164</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>3000</v>
-      </c>
+          <t>100nF</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="n">
         <v>2</v>
       </c>
@@ -1411,80 +1289,70 @@
       <c r="O11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0.2974</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0.5948</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0.5948</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PRTR5V0U2X</t>
+          <t>4.7uF</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-143</t>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>C2827688</t>
+          <t>C307331</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>TECH PUBLIC</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>PRTR5V0U2X</t>
+          <t>CL05B104KB54PNC</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+125℃ 0.3pF、0.8pF 100W 10V、15V 5V 6.5V 6A 80nA ESD IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 Three channels Unidirectional SOT-143 ESD and Surge Protection (TVS/ESD) ROHS</t>
+          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SOT-143</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>60459</v>
+        <v>8002097</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>2</v>
@@ -1500,17 +1368,17 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.0076</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>0.1218</t>
+          <t>0.0152</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0.1218</t>
+          <t>0.0152</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr"/>
@@ -1518,83 +1386,83 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>D13,D14,D15</t>
+          <t>C17,C19</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SS34_C8678</t>
+          <t>22u 25V</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:SMA_L4.3-W2.6-LS5.2-RD</t>
+          <t>Capacitor_SMD:C_1210_3225Metric</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>C8678</t>
+          <t>C52306</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MDD(Microdiode Semiconductor)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>SS34</t>
+          <t>CL32A226KAJNNNE</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+125℃ 3A 40V 500uA@40V 550mV@3A Independent SMA(DO-214AC) Schottky Diodes ROHS</t>
+          <t>22uF 25V X5R ±10% 1210 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SMA(DO-214AC)</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3735309</v>
+        <v>203545</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>0.0301</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>0.1806</t>
+          <t>0.7248</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0.1806</t>
+          <t>0.7248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr"/>
@@ -1602,42 +1470,42 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XH-2P-SMD</t>
+          <t>0.5pF</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_2P-P2.54_XH2.54-2AB</t>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>C146125</t>
+          <t>C778333</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>BOOMELE(Boom Precision Elec)</t>
+          <t>EYANG(Shenzhen Eyang Tech Development)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>XH-2PVertical welding</t>
+          <t>C0402C0G0R6B500NTB</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-25℃~+85℃ 1 12mm 1x2P 2 2.5mm 250V 2P 3A 6mm 7.8mm Beige LCP Phosphor bronze Surface Mount,Vertical Tin UL94V-0 XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
+          <t>0.6pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SMD,P=2.5mm</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1646,13 +1514,13 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>11017</v>
+        <v>250</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>57</v>
+        <v>10000</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>2</v>
@@ -1668,17 +1536,17 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0.0669</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.0058</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.0058</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr"/>
@@ -1686,42 +1554,42 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2.54-3P-LT</t>
+          <t>0.8pF</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_2.54-3P-LT</t>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>C2681544</t>
+          <t>C3875120</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SHOU HAN</t>
+          <t>Venkel</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2.54-3P LT</t>
+          <t>C0402C0G500-0R8BNP</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25℃~+85℃ 1 1x3P 2.5mm 250V 3 3A 3P Beige Brass LCP Surface Mount,Vertical Tin UL94V-0 XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
+          <t>0.8pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SMD,P=2.5mm</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1730,13 +1598,13 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1331</v>
+        <v>9750</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>2</v>
@@ -1752,17 +1620,17 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>0.0814</t>
+          <t>0.0105</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>0.1628</t>
+          <t>0.0210</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>0.1628</t>
+          <t>0.0210</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr"/>
@@ -1770,83 +1638,83 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>C27,C35</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SIM_Card</t>
+          <t>12pF</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:SIM-SMD_SMN-303</t>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>C266888</t>
+          <t>C1547</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>XUNPU</t>
+          <t>FH (Guangdong Fenghua Advanced Tech)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>SMN-303</t>
+          <t>0402CG120J500NT</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-25℃~+85℃ 1.37mm Connector and Ejector Nano-SIM Card Push-Push With Card Detect SMD SIM Card Connectors ROHS</t>
+          <t>12pF 50V C0G ±5% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SMD</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>119092</v>
+        <v>719856</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>0.4894</t>
+          <t>0.0036</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>0.9788</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0.9788</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr"/>
@@ -1854,42 +1722,42 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>L2,L3</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>10uH</t>
+          <t>B3B-PH-K-S</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:IND-SMD_L4.0-W4.0</t>
+          <t>easyeda2kicad:CONN-TH_B3B-PH-K-S</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>C2849472</t>
+          <t>C131339</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>DMBJ</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>PNLS4030-100M 10UH</t>
+          <t>B3B-PH-K-S(LF)(SN)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10uH 120mΩ 2A 2A Magnetic Shielded Inductor ±20% SMD,4x4mm Power Inductors ROHS</t>
+          <t>-25℃~+85℃ 1 100V 1x3P 2A 2mm 3 3P 4.5mm 6mm 7.9mm Brass K Pin PA66 PH Through Hole Tin UL94V-0 White 插件,P=2mm Wire To Board Connector ROHS</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SMD,4x4mm</t>
+          <t>Plugin,P=2mm</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1898,39 +1766,39 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10402</v>
+        <v>220423</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>0.0521</t>
+          <t>0.0412</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>0.2084</t>
+          <t>0.0824</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0.2084</t>
+          <t>0.0824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr"/>
@@ -1938,42 +1806,42 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>L4,L5</t>
+          <t>D1,D4,D6,D7,D8,D9,D10,D11</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2.2uH</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:IND-SMD_L4.0-W4.0_NRS4018T</t>
+          <t>easyeda2kicad:LED-SMD_L3.0-W3.0_XL-3030UWC-1W-3V</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>C92959</t>
+          <t>C2843891</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Taiyo Yuden</t>
+          <t>XINGLIGHT</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>NRS4018T2R2MDGJ</t>
+          <t>XL-3030UWC-1W-3V</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2.2A 2.2uH 3A 42mΩ ±20% SMD,4x4mm Power Inductors ROHS</t>
+          <t>-40℃~+85℃ 120° 1W 3.4V 350mA 6500K~7000K Discrete Diode Top-mount White Yellow Lens SMD3030-2P LED Indication - Discrete ROHS</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SMD,4x4mm</t>
+          <t>SMD3030-2P</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1982,39 +1850,39 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12164</v>
+        <v>167784</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>0.0886</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>0.3544</t>
+          <t>0.672</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0.3544</t>
+          <t>0.672</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr"/>
@@ -2022,58 +1890,28 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>4.7nH</t>
+          <t>BAV199DW</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:L0402-R-RD</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>C86065</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Murata Electronics</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>LQG15HS4N7S02D</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>160mΩ 4.7nH 6GHz 700mA 8@100MHz Multilayer inductor 0402 Inductors (SMD) ROHS</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>370072</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>10000</v>
-      </c>
+          <t>Package_TO_SOT_SMD:SOT-363_SC-70-6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="n">
         <v>2</v>
       </c>
@@ -2083,65 +1921,55 @@
       <c r="O19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0.046</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0.046</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>LED1,LED2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>19-237/R6GHBHC-A01/2T</t>
+          <t>SP3012-04UTG</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:LED-ARRAY-SMD_4P-L1.6-W1.6-BL_1</t>
+          <t>easyeda2kicad:UDFN-10_L2.5-W1.0-P0.50-BL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>C60105</t>
+          <t>C151304</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Everlight Elec</t>
+          <t>Littelfuse</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19-237/R6GHBHC-A01/2T</t>
+          <t>SP3012-04UTG</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>120° Common Anode SMD-4P,1.6x1.6mm RGB LEDs ROHS</t>
+          <t>-40℃~+125℃ 0.5pF 1.5uA 4A@8/20us 5V 8.4V ESD Four channels IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 UDFN-10(1x2.5) ESD and Surge Protection (TVS/ESD) ROHS</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SMD-4P,1.6x1.6mm</t>
+          <t>UDFN-10(1x2.5)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2150,39 +1978,39 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>52185</v>
+        <v>4564</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>0.2496</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0.2496</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr"/>
@@ -2190,42 +2018,42 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>USB_C_Plug_USB2.0</t>
+          <t>PRTR5V0U2X</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:TYPE-C-SMD_TYPE-C-6P_1</t>
+          <t>Package_TO_SOT_SMD:SOT-143</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>C456012</t>
+          <t>C2827688</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>SHOU HAN</t>
+          <t>TECH PUBLIC</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>TYPE-C 6P</t>
+          <t>PRTR5V0U2X</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-40℃~+85℃ 1 3,000 Cycles 3A 5V 6P Black Female Surface Mount, Right Angle Type-C SMD USB Connectors ROHS</t>
+          <t>-55℃~+125℃ 0.3pF、0.8pF 100W 10V、15V 5V 6.5V 6A 80nA ESD IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 Three channels Unidirectional SOT-143 ESD and Surge Protection (TVS/ESD) ROHS</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SMD</t>
+          <t>SOT-143</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2234,13 +2062,13 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>585486</v>
+        <v>56619</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>2</v>
@@ -2256,17 +2084,17 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>0.0770</t>
+          <t>0.1218</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0.0770</t>
+          <t>0.1218</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr"/>
@@ -2274,57 +2102,57 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Q1,Q2,Q4</t>
+          <t>D13,D14,D15</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BSS84</t>
+          <t>SS34_C8678</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>easyeda2kicad:SMA_L4.3-W2.6-LS5.2-RD</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>C3018484</t>
+          <t>C8678</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>FUXINSEMI</t>
+          <t>MDD(Microdiode Semiconductor)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>BSS84</t>
+          <t>SS34</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+150℃ 1 P-Channel 10pF 10Ω@5V 130mA 225mW 2V 30pF 50V 5pF SOT-23 MOSFETs ROHS</t>
+          <t>-55℃~+125℃ 3A 40V 500uA@40V 550mV@3A Independent SMA(DO-214AC) Schottky Diodes ROHS</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>SMA(DO-214AC)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18156</v>
+        <v>3689864</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>2</v>
@@ -2340,17 +2168,17 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>0.0223</t>
+          <t>0.0301</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1806</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr"/>
@@ -2358,83 +2186,83 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Q3,Q5,Q6</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>XH-2P-SMD</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>easyeda2kicad:CONN-SMD_2P-P2.54_XH2.54-2AB</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>C8545</t>
+          <t>C146125</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Jiangsu Changjing Electronics Technology Co., Ltd.</t>
+          <t>BOOMELE(Boom Precision Elec)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>XH-2PVertical welding</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1 N-channel 115mA 2.5V 225mW 50pF 5pF 5Ω@10V 60V SOT-23 MOSFETs ROHS</t>
+          <t>-25℃~+85℃ 1 12mm 1x2P 2 2.5mm 250V 2P 3A 6mm 7.8mm Beige LCP Phosphor bronze Surface Mount,Vertical Tin UL94V-0 XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>SMD,P=2.5mm</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>509621</v>
+        <v>10941</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>3000</v>
+        <v>57</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>0.0154</t>
+          <t>0.0668</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1336</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1336</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr"/>
@@ -2442,57 +2270,57 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>47k</t>
+          <t>2.54-3P-LT</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>easyeda2kicad:CONN-SMD_2.54-3P-LT</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>C25792</t>
+          <t>C2681544</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>SHOU HAN</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0402WGF4702TCE</t>
+          <t>2.54-3P LT</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 47kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>-25℃~+85℃ 1 1x3P 2.5mm 250V 3 3A 3P Beige Brass LCP Surface Mount,Vertical Tin UL94V-0 XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SMD,P=2.5mm</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1476306</v>
+        <v>1331</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>2</v>
@@ -2508,17 +2336,17 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>0.0012</t>
+          <t>0.0814</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>0.0024</t>
+          <t>0.1628</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0.0024</t>
+          <t>0.1628</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr"/>
@@ -2526,42 +2354,42 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>150k</t>
+          <t>SIM_Card</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>easyeda2kicad:SIM-SMD_SMN-303</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>C22369540</t>
+          <t>C266888</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>HKR(Hong Kong Resistors)</t>
+          <t>XUNPU</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>RCA02150KFLF</t>
+          <t>SMN-303</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 150kΩ 50V 62.5mW Thick Film Resistor ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>-25℃~+85℃ 1.37mm Connector and Ejector Nano-SIM Card Push-Push With Card Detect SMD SIM Card Connectors ROHS</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SMD</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2570,13 +2398,13 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>517</v>
+        <v>117712</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>2</v>
@@ -2592,17 +2420,17 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.4888</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>0.0008</t>
+          <t>0.9776</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0.0008</t>
+          <t>0.9776</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr"/>
@@ -2610,42 +2438,42 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>R3,R4,R20,R22</t>
+          <t>L2,L3</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>10uH</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>easyeda2kicad:IND-SMD_L4.0-W4.0</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>C49330233</t>
+          <t>C2849472</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>HKR(Hong Kong Resistors)</t>
+          <t>DMBJ</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>AS0210KF</t>
+          <t>PNLS4030-100M 10UH</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 10kΩ 50V 62.5mW ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>10uH 120mΩ 2A 2A Magnetic Shielded Inductor ±20% SMD,4x4mm Power Inductors ROHS</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SMD,4x4mm</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2654,39 +2482,39 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1820</v>
+        <v>10402</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O26" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="P26" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0.0016</t>
+          <t>0.052</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>0.0128</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0.0128</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr"/>
@@ -2694,83 +2522,83 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>R5,R6,R28</t>
+          <t>L4,L5</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>2.2uH</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>easyeda2kicad:IND-SMD_L4.0-W4.0_NRS4018T</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>C25104</t>
+          <t>C92959</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Taiyo Yuden</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0402WGF3300TCE</t>
+          <t>NRS4018T2R2MDGJ</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 330Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>2.2A 2.2uH 3A 42mΩ ±20% SMD,4x4mm Power Inductors ROHS</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SMD,4x4mm</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>918201</v>
+        <v>12084</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>0.0012</t>
+          <t>0.0884</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>0.3536</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>0.3536</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr"/>
@@ -2778,37 +2606,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>R7,R8,R9,R10,R11,R12,R13,R14</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.7nH</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>easyeda2kicad:L0402-R-RD</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>C25169</t>
+          <t>C86065</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Murata Electronics</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0402WGJ047JTCE</t>
+          <t>LQG15HS4N7S02D</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 4.7Ω 50V 62.5mW Thick Film Resistor ±200ppm/℃ ±5% 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>160mΩ 4.7nH 6GHz 700mA 8@100MHz Multilayer inductor 0402 Inductors (SMD) ROHS</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2822,7 +2650,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1975</v>
+        <v>369652</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>1</v>
@@ -2834,27 +2662,27 @@
         <v>2</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>0.0016</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>0.0256</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0.0256</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr"/>
@@ -2862,83 +2690,83 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>LED1,LED2</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>5.1k</t>
+          <t>19-237/R6GHBHC-A01/2T</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>easyeda2kicad:LED-ARRAY-SMD_4P-L1.6-W1.6-BL_1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>C25905</t>
+          <t>C60105</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Everlight Elec</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0402WGF5101TCE</t>
+          <t>19-237/R6GHBHC-A01/2T</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 5.1kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>120° Common Anode SMD-4P,1.6x1.6mm RGB LEDs ROHS</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SMD-4P,1.6x1.6mm</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2475295</v>
+        <v>52136</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>0.0009</t>
+          <t>0.0623</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>0.0018</t>
+          <t>0.2492</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0.0018</t>
+          <t>0.2492</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr"/>
@@ -2946,126 +2774,86 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>R16,R17</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>22R</t>
+          <t>AO3400A</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>C100318</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>LIZ Elec</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>CR0402FF22R0G</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+125℃ 22Ω 50V 62.5mW Thick Film Resistor ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1744</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>10000</v>
-      </c>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0.0006</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0.0024</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0.0024</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>R18,R23,R24</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>100R</t>
+          <t>2N7002</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>C25076</t>
+          <t>C8545</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Jiangsu Changjing Electronics Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0402WGF1000TCE</t>
+          <t>2N7002</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 100Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>1 N-channel 115mA 2.5V 225mW 50pF 5pF 5Ω@10V 60V SOT-23 MOSFETs ROHS</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3074,39 +2862,39 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3450166</v>
+        <v>499090</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>0.0012</t>
+          <t>0.0153</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>0.0306</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>0.0306</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr"/>
@@ -3114,12 +2902,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>191k</t>
+          <t>47k</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3129,22 +2917,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>C159084</t>
+          <t>C25792</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>RALEC</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>RTT021913FTH</t>
+          <t>0402WGF4702TCE</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 191kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>-55℃~+155℃ 47kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3154,11 +2942,11 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9213</v>
+        <v>1438416</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>1</v>
@@ -3180,17 +2968,17 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0012</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0024</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0024</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr"/>
@@ -3198,12 +2986,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>240k</t>
+          <t>330k</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3213,22 +3001,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>C64043</t>
+          <t>C22369540</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>HKR(Hong Kong Resistors)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0402WGF2403TCE</t>
+          <t>RCA02150KFLF</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 240kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>-55℃~+155℃ 150kΩ 50V 62.5mW Thick Film Resistor ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3242,7 +3030,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>5763</v>
+        <v>247</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>1</v>
@@ -3264,17 +3052,17 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.0008</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.0008</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr"/>
@@ -3282,12 +3070,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R3,R4,R20,R22</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3297,22 +3085,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>C144809</t>
+          <t>C49330233</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>HKR(Hong Kong Resistors)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>AC0402FR-07100KL</t>
+          <t>AS0210KF</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 100kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>-55℃~+155℃ 10kΩ 50V 62.5mW ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3326,10 +3114,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10265</v>
+        <v>10</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>5971</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>10000</v>
@@ -3338,27 +3126,27 @@
         <v>2</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>2</v>
+        <v>5971</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0.0018</t>
+          <t>0.0016</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0128</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>9.5536</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr"/>
@@ -3366,12 +3154,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>R26,R27</t>
+          <t>R5,R6,R28</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>330</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3381,7 +3169,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>C25900</t>
+          <t>C25104</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3391,12 +3179,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0402WGF4701TCE</t>
+          <t>0402WGF3300TCE</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-55℃~+155℃ 4.7kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+          <t>-55℃~+155℃ 330Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3410,7 +3198,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4025673</v>
+        <v>910091</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>1</v>
@@ -3422,27 +3210,27 @@
         <v>2</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0.0011</t>
+          <t>0.0012</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0072</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0072</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr"/>
@@ -3450,42 +3238,42 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RV1</t>
+          <t>R7,R8,R9,R10</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>22R</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:RES-ADJ-SMD_3P-L3.0-W3.8-P1.75-BR</t>
+          <t>Resistor_SMD:R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>C719176</t>
+          <t>C175252</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>BOURNS</t>
+          <t>Ever Ohms Tech</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TC33X-2-103E</t>
+          <t>CRH2512F22R0E04Z</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1 10kΩ 150mW ±25% ±250ppm/℃ SMD-3P,3.8x3.6mm Potentiometers, Variable Resistors ROHS</t>
+          <t>-55℃~+155℃ 200V 22Ω 2W Thick Film Resistor ±1% ±100ppm/℃ 2512 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SMD-3P,3.8x3.6mm</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3494,39 +3282,39 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>73160</v>
+        <v>1329</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0.1065</t>
+          <t>0.0589</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>0.2130</t>
+          <t>0.4712</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0.2130</t>
+          <t>0.4712</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr"/>
@@ -3534,58 +3322,24 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SW_Push</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>easyeda2kicad:KEY-SMD_4P-L4.2-W3.2-P2.20-LS4.6</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>C139797</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>ALPSALPINE</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>SKRPACE010</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>-30℃~+85℃ 16V 2.5mm 2.6N 3.2mm 4.2mm 50,000 cycles 50mA J-Lead Oval button SPST-NO Surface Mount,Vertical SMD-4P,4.2x3.2mm Tactile Switches ROHS</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>SMD-4P,4.2x3.2mm</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>129256</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>4000</v>
-      </c>
+          <t>150R</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="n">
         <v>2</v>
       </c>
@@ -3595,248 +3349,150 @@
       <c r="O37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0.0629</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0.1258</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0.1258</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TH1</t>
+          <t>R12,R16,R17</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Thermistor</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>C77131</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Murata Electronics</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>NCP15XH103F03RC</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+125℃ 0.5mm 100mW 10kΩ 1mW/℃ 1mm 310uA 3380K 3434K 3455K ±1% ±1% 0402 NTC Thermistors ROHS</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>149938</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>10000</v>
-      </c>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>0.0199</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>0.0398</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0.0398</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R15,R29</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>nRF52840</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Package_DFN_QFN:Nordic_AQFN-73-1EP_7x7mm_P0.5mm</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>C190794</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Nordic Semicon</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>NRF52840-QIAA-R</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>-95dBm 1.7V~5.5V 2.4GHz 2.4GHz~2.4835GHz 2Mbps 4.82mA 6.26mA 8dBm SPI、USB、UART、ADC、I2S、PWM ZigBee、Bluetooth、LoRa、ISM transceiver AQFN-73-EP(7x7) RF Transceiver ICs ROHS</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>AQFN-73-EP(7x7)</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>31360</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>3000</v>
-      </c>
+          <t>100k</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>5.7384</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>11.4768</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>11.4768</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>NRF9151-LACA-R7</t>
+          <t>100R</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:LGA-113_L12.1-W11.1_NRF9151-LACA-R7</t>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>C22397843</t>
+          <t>C25076</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nordic Semicon</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>nRF9151-LACA-R7</t>
+          <t>0402WGF1000TCE</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>LGA-113(12.1x11.1) RF Modules ROHS</t>
+          <t>-55℃~+155℃ 100Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>LGA-113(12.1x11.1)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>523</v>
+        <v>3351927</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>2</v>
@@ -3852,17 +3508,17 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>16.1428</t>
+          <t>0.0012</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>32.2856</t>
+          <t>0.0024</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>32.2856</t>
+          <t>0.0024</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr"/>
@@ -3870,42 +3526,42 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>NPM1300</t>
+          <t>191k</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:BGA-35_L3.1-W2.4-R5-C7-P0.42_NPM1300-CAAA-R</t>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>C25346894</t>
+          <t>C159084</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Nordic Semicon</t>
+          <t>RALEC</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>NPM1300-CAAA-R7</t>
+          <t>RTT021913FTH</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>WLCSP-35(2.4x3.1) Power Management - Specialized ROHS</t>
+          <t>-55℃~+155℃ 191kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>WLCSP-35(2.4x3.1)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3914,13 +3570,13 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>282</v>
+        <v>9213</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>2</v>
@@ -3936,17 +3592,17 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>2.5632</t>
+          <t>0.0007</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>5.1264</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5.1264</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr"/>
@@ -3954,42 +3610,42 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BMA400</t>
+          <t>240k</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:LGA-12_L2.0-W2.0-P0.50-BL</t>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>C437655</t>
+          <t>C64043</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Bosch Sensortec</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>BMA400</t>
+          <t>0402WGF2403TCE</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-40℃~+85℃ 1.71V~3.6V 12bit 160nA 1KB Accelerometer SPI、I2C X,Y,Z ±16g LGA-12(2x2) Accelerometers ROHS</t>
+          <t>-55℃~+155℃ 240kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>LGA-12(2x2)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -3998,7 +3654,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5405</v>
+        <v>5306</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>1</v>
@@ -4020,17 +3676,17 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2.3952</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4.7904</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4.7904</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr"/>
@@ -4038,142 +3694,64 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>U6,U10</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BWU.FL-IPEX1</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>easyeda2kicad:IPEX-SMD_BWIPX-1-001E</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>C5137195</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>BAT WIRELESS</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>BWU.FL-IPEX1</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>1 1.25mm 2mm 50Ω 6GHz Board Side IPEX Male Pin SMD Coaxial Connectors (RF) ROHS</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>711347</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>5000</v>
-      </c>
+          <t>18k</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0.0398</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0.1592</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0.1592</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>AN6520-245</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>easyeda2kicad:ANT-SMD_L6.5-W2.0</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>C239238</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Rainsun microwave Tech</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>AN6520-245</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+85℃ 0.5dBi 1mm 2 2.2mm 2.45GHz 200MHz 3W 50Ω 6.5mm SMD Antennas ROHS</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>1893</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>1500</v>
-      </c>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="n">
         <v>2</v>
       </c>
@@ -4183,65 +3761,55 @@
       <c r="O44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>0.5734</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1.1468</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1.1468</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SEN0348_CONN</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_SM06B-SRSS-TB-LF-SN</t>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>C160405</t>
+          <t>C144809</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>SM06B-SRSS-TB(LF)(SN)</t>
+          <t>AC0402FR-07100KL</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-25℃~+85℃ 1 1A 1mm 1x6P 2.9mm 4.32mm 50V 6 6P 8mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
+          <t>-55℃~+155℃ 100kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -4250,13 +3818,13 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>65536</v>
+        <v>10000</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>2</v>
@@ -4272,17 +3840,17 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0.2998</t>
+          <t>0.0018</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>0.5996</t>
+          <t>0.0036</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>0.5996</t>
+          <t>0.0036</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr"/>
@@ -4290,83 +3858,83 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>R26,R27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>C160404</t>
+          <t>C25900</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB(LF)(SN)</t>
+          <t>0402WGF4701TCE</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-25℃~+85℃ 1 1A 1mm 1x4P 2.9mm 4 4.32mm 4P 50V 6mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
+          <t>-55℃~+155℃ 4.7kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>10042</v>
+        <v>3855293</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>0.2245</t>
+          <t>0.0011</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>0.4490</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>0.4490</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr"/>
@@ -4374,126 +3942,86 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>U11,U14</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>HX PZ1.27-2x5P TP</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:HDR-SMD_10P-P1.27-V-M-R2-C5-LS5.5_1</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>C41376037</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>hanxia</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>HX PZ1.27-2x5P TP</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+105℃ 1.27mm 1.27mm 10P 1A 1mm 2 2x5P 4mm 500V Black Brass Gold Pin Header Surface Mount,Vertical SMD,P=1.27mm Pin Headers ROHS</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>SMD,P=1.27mm</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>14553</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>1000</v>
-      </c>
+          <t>Resistor_SMD:R_01005_0402Metric</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>0.096</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>0.384</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0.384</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>U12,U13</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MT3608</t>
+          <t>SW_Push</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
+          <t>easyeda2kicad:KEY-SMD_4P-L4.2-W3.2-P2.20-LS4.6</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>C84817</t>
+          <t>C139797</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>XI'AN Aerosemi Tech</t>
+          <t>ALPSALPINE</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>MT3608</t>
+          <t>SKRPACE010</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-40℃~+85℃ 1 1.2MHz 100uA、1.6mA 2A 2V~24V Adjustable Boost Boost Built-in No SOT-23-6 DC-DC Converters ROHS</t>
+          <t>-30℃~+85℃ 16V 2.5mm 2.6N 3.2mm 4.2mm 50,000 cycles 50mA J-Lead Oval button SPST-NO Surface Mount,Vertical SMD-4P,4.2x3.2mm Tactile Switches ROHS</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>SMD-4P,4.2x3.2mm</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -4502,39 +4030,39 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>182531</v>
+        <v>127609</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0628</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.1256</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.1256</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr"/>
@@ -4542,89 +4070,1137 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>TP1,TP2,TP3</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>nRF52840</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Package_DFN_QFN:Nordic_AQFN-73-1EP_7x7mm_P0.5mm</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>C190794</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>NRF52840-QIAA-R</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>-95dBm 1.7V~5.5V 2.4GHz 2.4GHz~2.4835GHz 2Mbps 4.82mA 6.26mA 8dBm SPI、USB、UART、ADC、I2S、PWM ZigBee、Bluetooth、LoRa、ISM transceiver AQFN-73-EP(7x7) RF Transceiver ICs ROHS</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>AQFN-73-EP(7x7)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>31307</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>5.7315</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>11.4630</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>11.4630</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>NRF9151-LACA-R7</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:LGA-113_L12.1-W11.1_NRF9151-LACA-R7</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>C22397843</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>nRF9151-LACA-R7</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>LGA-113(12.1x11.1) RF Modules ROHS</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>LGA-113(12.1x11.1)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>16.1232</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>32.2464</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>32.2464</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>NPM1300</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:BGA-35_L3.1-W2.4-R5-C7-P0.42_NPM1300-CAAA-R</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>C25346894</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>NPM1300-CAAA-R7</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>WLCSP-35(2.4x3.1) Power Management - Specialized ROHS</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>WLCSP-35(2.4x3.1)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>2.6665</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>5.3330</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>5.3330</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>BMA400</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:LGA-12_L2.0-W2.0-P0.50-BL</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>C437655</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Bosch Sensortec</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>BMA400</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 1.71V~3.6V 12bit 160nA 1KB Accelerometer SPI、I2C X,Y,Z ±16g LGA-12(2x2) Accelerometers ROHS</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>LGA-12(2x2)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>5400</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>2.3923</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>4.7846</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>4.7846</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>DRV8871DDA</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Package_SO:Texas_HTSOP-8-1EP_3.9x4.9mm_P1.27mm_EP2.95x4.9mm_Mask2.4x3.1mm_ThermalVias</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>U6,U10</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>BWU.FL-IPEX1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:IPEX-SMD_BWIPX-1-001E</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>C5137195</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>BAT WIRELESS</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>BWU.FL-IPEX1</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1 1.25mm 2mm 50Ω 6GHz Board Side IPEX Male Pin SMD Coaxial Connectors (RF) ROHS</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>708917</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.0397</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>0.1588</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>0.1588</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>AN6520-245</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:ANT-SMD_L6.5-W2.0</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>C239238</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Rainsun microwave Tech</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>AN6520-245</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 0.5dBi 1mm 2 2.2mm 2.45GHz 200MHz 3W 50Ω 6.5mm SMD Antennas ROHS</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.5727</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>1.1454</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>1.1454</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SEN0348_CONN</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:CONN-SMD_SM06B-SRSS-TB-LF-SN</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>C160405</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>SM06B-SRSS-TB(LF)(SN)</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1A 1mm 1x6P 2.9mm 4.32mm 50V 6 6P 8mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>65256</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.2994</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>0.5988</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>0.5988</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM04B-SRSS-TB</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>C160404</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>SM04B-SRSS-TB(LF)(SN)</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1A 1mm 1x4P 2.9mm 4 4.32mm 4P 50V 6mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>9497</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.2243</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>0.4486</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>8.9720</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>U11,U14</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>HX PZ1.27-2x5P TP</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:HDR-SMD_10P-P1.27-V-M-R2-C5-LS5.5_1</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>C41376037</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>hanxia</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>HX PZ1.27-2x5P TP</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+105℃ 1.27mm 1.27mm 10P 1A 1mm 2 2x5P 4mm 500V Black Brass Gold Pin Header Surface Mount,Vertical SMD,P=1.27mm Pin Headers ROHS</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=1.27mm</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>14523</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.0959</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>0.3836</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>0.3836</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>U12,U13</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>MT3608</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>C84817</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>XI'AN Aerosemi Tech</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>MT3608</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 1 1.2MHz 100uA、1.6mA 2A 2V~24V Adjustable Boost Boost Built-in No SOT-23-6 DC-DC Converters ROHS</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23-6</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>288960</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.0799</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>0.3196</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>0.3196</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>USB1</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>TYPE-C 16PIN 2MD</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:USB-C-SMD_TYPE-C-16PIN-2MD-073</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>C2765186</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>SHOU HAN</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>TYPE-C 16PIN 2MD(073)</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 16P 3A 5,000 times 5V Black Female Surface Mount, Right Angle Type-C SMD USB Connectors ROHS</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>1378996</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.0736</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>0.1472</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>0.1472</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>32MHz</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>easyeda2kicad:CRYSTAL-SMD_4P-L2.0-W1.6-BL</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>C187794</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Seiko Epson</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Q22FA12800025</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>-20℃~+75℃ 32MHz 60Ω 8pF Crystal Oscillator ±10ppm ±10ppm SMD2016-4P Crystals ROHS</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SMD2016-4P</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>Extended</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n">
-        <v>14435</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="2" t="n">
+      <c r="J62" s="2" t="n">
+        <v>14395</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="M49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>0.2321</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>0.4642</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>0.4642</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>0.2319</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>0.4638</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>0.4638</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>32.768kHz</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>No LCSC/JLCPCB part selected yet.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T49"/>
+  <autoFilter ref="A1:T63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/bom/smart_pouch_technical_reference.xlsx
+++ b/bom/smart_pouch_technical_reference.xlsx
@@ -471,10 +471,10 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -612,40 +612,14 @@
           <t>C307331</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>CL05B104KB54PNC</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>8002097</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="n">
         <v>2</v>
       </c>
@@ -658,21 +632,9 @@
       <c r="P2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>0.0076</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>0.1064</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>0.1064</t>
-        </is>
-      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -696,40 +658,14 @@
           <t>C52923</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>CL05A105KA5NQNC</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1uF 25V X5R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>3365443</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="n">
         <v>2</v>
       </c>
@@ -742,21 +678,9 @@
       <c r="P3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>0.0142</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>0.0852</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>0.0852</t>
-        </is>
-      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
@@ -860,40 +784,14 @@
           <t>C15850</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>CL21A106KAYNNNE</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>3203459</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="n">
         <v>2</v>
       </c>
@@ -906,21 +804,9 @@
       <c r="P6" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0.0767</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1.0738</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1.0738</t>
-        </is>
-      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
@@ -944,40 +830,14 @@
           <t>C15850</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>CL21A106KAYNNNE</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>3203459</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="n">
         <v>2</v>
       </c>
@@ -990,21 +850,9 @@
       <c r="P7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0.0767</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0.3068</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0.3068</t>
-        </is>
-      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1028,40 +876,14 @@
           <t>C307331</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>CL05B104KB54PNC</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>8002097</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="n">
         <v>2</v>
       </c>
@@ -1074,21 +896,9 @@
       <c r="P8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0.0076</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0.0152</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0.0152</t>
-        </is>
-      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1112,40 +922,14 @@
           <t>C52923</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>CL05A105KA5NQNC</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1uF 25V X5R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>3365443</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="n">
         <v>2</v>
       </c>
@@ -1158,21 +942,9 @@
       <c r="P9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0.0142</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0.0284</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0.0284</t>
-        </is>
-      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1196,40 +968,14 @@
           <t>C307331</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>CL05B104KB54PNC</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>8002097</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="n">
         <v>2</v>
       </c>
@@ -1242,21 +988,9 @@
       <c r="P10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0.0076</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0.0152</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0.0152</t>
-        </is>
-      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1320,40 +1054,14 @@
           <t>C307331</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>CL05B104KB54PNC</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>8002097</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n">
         <v>2</v>
       </c>
@@ -1366,21 +1074,9 @@
       <c r="P12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0.0076</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0.0152</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0.0152</t>
-        </is>
-      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1404,40 +1100,14 @@
           <t>C52306</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>CL32A226KAJNNNE</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22uF 25V X5R ±10% 1210 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1210</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>203545</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>1000</v>
-      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="n">
         <v>2</v>
       </c>
@@ -1450,21 +1120,9 @@
       <c r="P13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0.1812</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0.7248</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0.7248</t>
-        </is>
-      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1488,40 +1146,14 @@
           <t>C778333</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>EYANG(Shenzhen Eyang Tech Development)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>C0402C0G0R6B500NTB</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0.6pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="n">
         <v>2</v>
       </c>
@@ -1534,21 +1166,9 @@
       <c r="P14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0.0029</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0.0058</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0.0058</t>
-        </is>
-      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1572,40 +1192,14 @@
           <t>C3875120</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Venkel</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>C0402C0G500-0R8BNP</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0.8pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>9750</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="n">
         <v>2</v>
       </c>
@@ -1618,21 +1212,9 @@
       <c r="P15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0.0105</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0.0210</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0.0210</t>
-        </is>
-      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1656,40 +1238,14 @@
           <t>C1547</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>FH (Guangdong Fenghua Advanced Tech)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0402CG120J500NT</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12pF 50V C0G ±5% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>719856</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="n">
         <v>2</v>
       </c>
@@ -1702,21 +1258,9 @@
       <c r="P16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0.0036</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0.0144</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0.0144</t>
-        </is>
-      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1740,40 +1284,14 @@
           <t>C131339</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>JST</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>B3B-PH-K-S(LF)(SN)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-25℃~+85℃ 1 100V 1x3P 2A 2mm 3 3P 4.5mm 6mm 7.9mm Brass K Pin PA66 PH Through Hole Tin UL94V-0 White 插件,P=2mm Wire To Board Connector ROHS</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Plugin,P=2mm</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>220423</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>1000</v>
-      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="n">
         <v>2</v>
       </c>
@@ -1786,21 +1304,9 @@
       <c r="P17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0.0412</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0.0824</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0.0824</t>
-        </is>
-      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1824,40 +1330,14 @@
           <t>C2843891</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>XINGLIGHT</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>XL-3030UWC-1W-3V</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+85℃ 120° 1W 3.4V 350mA 6500K~7000K Discrete Diode Top-mount White Yellow Lens SMD3030-2P LED Indication - Discrete ROHS</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>SMD3030-2P</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>167784</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="n">
         <v>2</v>
       </c>
@@ -1870,21 +1350,9 @@
       <c r="P18" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>0.672</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0.672</t>
-        </is>
-      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1952,40 +1420,14 @@
           <t>C151304</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Littelfuse</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>SP3012-04UTG</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+125℃ 0.5pF 1.5uA 4A@8/20us 5V 8.4V ESD Four channels IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 UDFN-10(1x2.5) ESD and Surge Protection (TVS/ESD) ROHS</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>UDFN-10(1x2.5)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>4564</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
         <v>2</v>
       </c>
@@ -1998,21 +1440,9 @@
       <c r="P20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0.297</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0.594</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0.594</t>
-        </is>
-      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2036,40 +1466,14 @@
           <t>C2827688</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>TECH PUBLIC</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>PRTR5V0U2X</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+125℃ 0.3pF、0.8pF 100W 10V、15V 5V 6.5V 6A 80nA ESD IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 Three channels Unidirectional SOT-143 ESD and Surge Protection (TVS/ESD) ROHS</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>SOT-143</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>56619</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="n">
         <v>2</v>
       </c>
@@ -2082,21 +1486,9 @@
       <c r="P21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>0.0609</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>0.1218</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0.1218</t>
-        </is>
-      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
@@ -2120,40 +1512,14 @@
           <t>C8678</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>MDD(Microdiode Semiconductor)</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>SS34</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+125℃ 3A 40V 500uA@40V 550mV@3A Independent SMA(DO-214AC) Schottky Diodes ROHS</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>SMA(DO-214AC)</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>3689864</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="n">
         <v>2</v>
       </c>
@@ -2166,21 +1532,9 @@
       <c r="P22" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0.0301</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0.1806</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0.1806</t>
-        </is>
-      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2204,40 +1558,14 @@
           <t>C146125</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>BOOMELE(Boom Precision Elec)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>XH-2PVertical welding</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-25℃~+85℃ 1 12mm 1x2P 2 2.5mm 250V 2P 3A 6mm 7.8mm Beige LCP Phosphor bronze Surface Mount,Vertical Tin UL94V-0 XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>SMD,P=2.5mm</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>10941</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>57</v>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="n">
         <v>2</v>
       </c>
@@ -2250,21 +1578,9 @@
       <c r="P23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0.0668</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0.1336</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0.1336</t>
-        </is>
-      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2288,40 +1604,14 @@
           <t>C2681544</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>SHOU HAN</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2.54-3P LT</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-25℃~+85℃ 1 1x3P 2.5mm 250V 3 3A 3P Beige Brass LCP Surface Mount,Vertical Tin UL94V-0 XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>SMD,P=2.5mm</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>1331</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>500</v>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="n">
         <v>2</v>
       </c>
@@ -2334,21 +1624,9 @@
       <c r="P24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0.0814</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0.1628</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0.1628</t>
-        </is>
-      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2372,40 +1650,14 @@
           <t>C266888</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>XUNPU</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>SMN-303</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>-25℃~+85℃ 1.37mm Connector and Ejector Nano-SIM Card Push-Push With Card Detect SMD SIM Card Connectors ROHS</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>117712</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>1500</v>
-      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="n">
         <v>2</v>
       </c>
@@ -2418,21 +1670,9 @@
       <c r="P25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>0.4888</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>0.9776</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0.9776</t>
-        </is>
-      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2456,40 +1696,14 @@
           <t>C2849472</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>DMBJ</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>PNLS4030-100M 10UH</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>10uH 120mΩ 2A 2A Magnetic Shielded Inductor ±20% SMD,4x4mm Power Inductors ROHS</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>SMD,4x4mm</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>10402</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="n">
         <v>2</v>
       </c>
@@ -2502,21 +1716,9 @@
       <c r="P26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>0.052</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>0.208</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0.208</t>
-        </is>
-      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2540,40 +1742,14 @@
           <t>C92959</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Taiyo Yuden</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>NRS4018T2R2MDGJ</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2.2A 2.2uH 3A 42mΩ ±20% SMD,4x4mm Power Inductors ROHS</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>SMD,4x4mm</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>12084</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>3500</v>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="n">
         <v>2</v>
       </c>
@@ -2586,21 +1762,9 @@
       <c r="P27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>0.0884</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>0.3536</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0.3536</t>
-        </is>
-      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2624,40 +1788,14 @@
           <t>C86065</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Murata Electronics</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>LQG15HS4N7S02D</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>160mΩ 4.7nH 6GHz 700mA 8@100MHz Multilayer inductor 0402 Inductors (SMD) ROHS</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>369652</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="n">
         <v>2</v>
       </c>
@@ -2670,21 +1808,9 @@
       <c r="P28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0.046</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0.046</t>
-        </is>
-      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2708,40 +1834,14 @@
           <t>C60105</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Everlight Elec</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>19-237/R6GHBHC-A01/2T</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>120° Common Anode SMD-4P,1.6x1.6mm RGB LEDs ROHS</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>SMD-4P,1.6x1.6mm</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>52136</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="n">
         <v>2</v>
       </c>
@@ -2754,21 +1854,9 @@
       <c r="P29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0.0623</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0.2492</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0.2492</t>
-        </is>
-      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2836,40 +1924,14 @@
           <t>C8545</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Jiangsu Changjing Electronics Technology Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>2N7002</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>1 N-channel 115mA 2.5V 225mW 50pF 5pF 5Ω@10V 60V SOT-23 MOSFETs ROHS</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>SOT-23</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>499090</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="n">
         <v>2</v>
       </c>
@@ -2882,21 +1944,9 @@
       <c r="P31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>0.0153</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>0.0306</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0.0306</t>
-        </is>
-      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2920,40 +1970,14 @@
           <t>C25792</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0402WGF4702TCE</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 47kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>1438416</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="n">
         <v>2</v>
       </c>
@@ -2966,21 +1990,9 @@
       <c r="P32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0.0024</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0.0024</t>
-        </is>
-      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
@@ -3004,40 +2016,14 @@
           <t>C22369540</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>HKR(Hong Kong Resistors)</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>RCA02150KFLF</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 150kΩ 50V 62.5mW Thick Film Resistor ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>247</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="n">
         <v>2</v>
       </c>
@@ -3050,21 +2036,9 @@
       <c r="P33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>0.0004</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>0.0008</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>0.0008</t>
-        </is>
-      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
@@ -3088,40 +2062,14 @@
           <t>C49330233</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>HKR(Hong Kong Resistors)</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>AS0210KF</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 10kΩ 50V 62.5mW ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>5971</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="n">
         <v>2</v>
       </c>
@@ -3132,23 +2080,11 @@
         <v>8</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>5971</v>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0.0016</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0.0128</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>9.5536</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -3172,40 +2108,14 @@
           <t>C25104</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>0402WGF3300TCE</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 330Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>910091</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="n">
         <v>2</v>
       </c>
@@ -3218,21 +2128,9 @@
       <c r="P35" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0.0072</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0.0072</t>
-        </is>
-      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
@@ -3256,40 +2154,14 @@
           <t>C175252</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Ever Ohms Tech</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>CRH2512F22R0E04Z</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 200V 22Ω 2W Thick Film Resistor ±1% ±100ppm/℃ 2512 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>2512</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>1329</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>4000</v>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="n">
         <v>2</v>
       </c>
@@ -3302,21 +2174,9 @@
       <c r="P36" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>0.0589</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>0.4712</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0.4712</t>
-        </is>
-      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
@@ -3460,40 +2320,14 @@
           <t>C25076</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>0402WGF1000TCE</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 100Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>3351927</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="n">
         <v>2</v>
       </c>
@@ -3506,21 +2340,9 @@
       <c r="P40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0.0024</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0.0024</t>
-        </is>
-      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3544,40 +2366,14 @@
           <t>C159084</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>RALEC</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>RTT021913FTH</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 191kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>9213</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="n">
         <v>2</v>
       </c>
@@ -3590,21 +2386,9 @@
       <c r="P41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0.0007</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0.0014</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0.0014</t>
-        </is>
-      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -3628,40 +2412,14 @@
           <t>C64043</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>0402WGF2403TCE</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 240kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>5306</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="n">
         <v>2</v>
       </c>
@@ -3674,21 +2432,9 @@
       <c r="P42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3792,40 +2538,14 @@
           <t>C144809</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>YAGEO</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>AC0402FR-07100KL</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 100kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="n">
         <v>2</v>
       </c>
@@ -3838,21 +2558,9 @@
       <c r="P45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>0.0018</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>0.0036</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>0.0036</t>
-        </is>
-      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
@@ -3876,40 +2584,14 @@
           <t>C25900</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>0402WGF4701TCE</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>-55℃~+155℃ 4.7kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>3855293</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="n">
         <v>2</v>
       </c>
@@ -3922,21 +2604,9 @@
       <c r="P46" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>0.0011</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>0.0044</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0.0044</t>
-        </is>
-      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
@@ -4004,40 +2674,14 @@
           <t>C139797</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>ALPSALPINE</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>SKRPACE010</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>-30℃~+85℃ 16V 2.5mm 2.6N 3.2mm 4.2mm 50,000 cycles 50mA J-Lead Oval button SPST-NO Surface Mount,Vertical SMD-4P,4.2x3.2mm Tactile Switches ROHS</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>SMD-4P,4.2x3.2mm</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>127609</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>4000</v>
-      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="n">
         <v>2</v>
       </c>
@@ -4050,21 +2694,9 @@
       <c r="P48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>0.0628</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>0.1256</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>0.1256</t>
-        </is>
-      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
@@ -4128,40 +2760,14 @@
           <t>C190794</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Nordic Semicon</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>NRF52840-QIAA-R</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>-95dBm 1.7V~5.5V 2.4GHz 2.4GHz~2.4835GHz 2Mbps 4.82mA 6.26mA 8dBm SPI、USB、UART、ADC、I2S、PWM ZigBee、Bluetooth、LoRa、ISM transceiver AQFN-73-EP(7x7) RF Transceiver ICs ROHS</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>AQFN-73-EP(7x7)</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>31307</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="n">
         <v>2</v>
       </c>
@@ -4174,21 +2780,9 @@
       <c r="P50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>5.7315</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>11.4630</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>11.4630</t>
-        </is>
-      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
@@ -4212,40 +2806,14 @@
           <t>C22397843</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Nordic Semicon</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>nRF9151-LACA-R7</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>LGA-113(12.1x11.1) RF Modules ROHS</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>LGA-113(12.1x11.1)</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>505</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>100</v>
-      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="n">
         <v>2</v>
       </c>
@@ -4258,21 +2826,9 @@
       <c r="P51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>16.1232</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>32.2464</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>32.2464</t>
-        </is>
-      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
       <c r="T51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
@@ -4296,40 +2852,14 @@
           <t>C25346894</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Nordic Semicon</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>NPM1300-CAAA-R7</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>WLCSP-35(2.4x3.1) Power Management - Specialized ROHS</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>WLCSP-35(2.4x3.1)</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>282</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>1500</v>
-      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="n">
         <v>2</v>
       </c>
@@ -4342,21 +2872,9 @@
       <c r="P52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>2.6665</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>5.3330</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>5.3330</t>
-        </is>
-      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
       <c r="T52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
@@ -4380,40 +2898,14 @@
           <t>C437655</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Bosch Sensortec</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>BMA400</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+85℃ 1.71V~3.6V 12bit 160nA 1KB Accelerometer SPI、I2C X,Y,Z ±16g LGA-12(2x2) Accelerometers ROHS</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>LGA-12(2x2)</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>5400</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="n">
         <v>2</v>
       </c>
@@ -4426,21 +2918,9 @@
       <c r="P53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>2.3923</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>4.7846</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>4.7846</t>
-        </is>
-      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
       <c r="T53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
@@ -4508,40 +2988,14 @@
           <t>C5137195</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>BAT WIRELESS</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>BWU.FL-IPEX1</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>1 1.25mm 2mm 50Ω 6GHz Board Side IPEX Male Pin SMD Coaxial Connectors (RF) ROHS</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>708917</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="n">
         <v>2</v>
       </c>
@@ -4554,21 +3008,9 @@
       <c r="P55" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>0.0397</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>0.1588</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>0.1588</t>
-        </is>
-      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
       <c r="T55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
@@ -4592,40 +3034,14 @@
           <t>C239238</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Rainsun microwave Tech</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>AN6520-245</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+85℃ 0.5dBi 1mm 2 2.2mm 2.45GHz 200MHz 3W 50Ω 6.5mm SMD Antennas ROHS</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>1893</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>1500</v>
-      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="n">
         <v>2</v>
       </c>
@@ -4638,21 +3054,9 @@
       <c r="P56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>0.5727</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>1.1454</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>1.1454</t>
-        </is>
-      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
       <c r="T56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
@@ -4676,40 +3080,14 @@
           <t>C160405</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>JST</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>SM06B-SRSS-TB(LF)(SN)</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>-25℃~+85℃ 1 1A 1mm 1x6P 2.9mm 4.32mm 50V 6 6P 8mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>65256</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="n">
         <v>2</v>
       </c>
@@ -4722,21 +3100,9 @@
       <c r="P57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>0.2994</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>0.5988</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr">
-        <is>
-          <t>0.5988</t>
-        </is>
-      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
       <c r="T57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
@@ -4760,40 +3126,14 @@
           <t>C160404</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>JST</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>SM04B-SRSS-TB(LF)(SN)</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>-25℃~+85℃ 1 1A 1mm 1x4P 2.9mm 4 4.32mm 4P 50V 6mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>9497</v>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="n">
         <v>2</v>
       </c>
@@ -4804,23 +3144,11 @@
         <v>2</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>0.2243</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>0.4486</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>8.9720</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
       <c r="T58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
@@ -4844,40 +3172,14 @@
           <t>C41376037</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>hanxia</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>HX PZ1.27-2x5P TP</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+105℃ 1.27mm 1.27mm 10P 1A 1mm 2 2x5P 4mm 500V Black Brass Gold Pin Header Surface Mount,Vertical SMD,P=1.27mm Pin Headers ROHS</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>SMD,P=1.27mm</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>14523</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>1000</v>
-      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="n">
         <v>2</v>
       </c>
@@ -4890,21 +3192,9 @@
       <c r="P59" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>0.0959</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>0.3836</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>0.3836</t>
-        </is>
-      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
       <c r="T59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
@@ -4928,40 +3218,14 @@
           <t>C84817</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>XI'AN Aerosemi Tech</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>MT3608</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>-40℃~+85℃ 1 1.2MHz 100uA、1.6mA 2A 2V~24V Adjustable Boost Boost Built-in No SOT-23-6 DC-DC Converters ROHS</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>SOT-23-6</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>288960</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="n">
         <v>2</v>
       </c>
@@ -4974,21 +3238,9 @@
       <c r="P60" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>0.0799</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>0.3196</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>0.3196</t>
-        </is>
-      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
       <c r="T60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
@@ -5012,40 +3264,14 @@
           <t>C2765186</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>SHOU HAN</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>TYPE-C 16PIN 2MD(073)</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>-25℃~+85℃ 1 16P 3A 5,000 times 5V Black Female Surface Mount, Right Angle Type-C SMD USB Connectors ROHS</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>1378996</v>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>1000</v>
-      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="n">
         <v>2</v>
       </c>
@@ -5058,21 +3284,9 @@
       <c r="P61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>0.0736</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>0.1472</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>0.1472</t>
-        </is>
-      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
       <c r="T61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
@@ -5096,40 +3310,14 @@
           <t>C187794</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Seiko Epson</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Q22FA12800025</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>-20℃~+75℃ 32MHz 60Ω 8pF Crystal Oscillator ±10ppm ±10ppm SMD2016-4P Crystals ROHS</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>SMD2016-4P</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>14395</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="n">
         <v>2</v>
       </c>
@@ -5142,21 +3330,9 @@
       <c r="P62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>0.2319</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>0.4638</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="inlineStr">
-        <is>
-          <t>0.4638</t>
-        </is>
-      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
       <c r="T62" s="2" t="inlineStr"/>
     </row>
     <row r="63">

--- a/bom/smart_pouch_technical_reference.xlsx
+++ b/bom/smart_pouch_technical_reference.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reference'!$A$1:$T$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reference'!$A$1:$T$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -147,8 +147,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReferenceTable" displayName="ReferenceTable" ref="A1:T63" headerRowCount="1">
-  <autoFilter ref="A1:T63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReferenceTable" displayName="ReferenceTable" ref="A1:T60" headerRowCount="1">
+  <autoFilter ref="A1:T60"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Designators"/>
     <tableColumn id="2" name="Value"/>
@@ -464,17 +464,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T63"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -486,7 +486,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -594,12 +594,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C1,C6,C8,C29,C30,C31,C32</t>
+          <t>C2,C5,C24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -609,43 +609,85 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>C307331</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>C52923</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>CL05A105KA5NQNC</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1uF 25V X5R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>3347699</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0.0142</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>0.0852</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>0.0852</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic 1uF 25V X5R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>C2,C5,C24</t>
+          <t>C3,C14,C36</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -655,17 +697,43 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>C52923</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>C1525</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>CL05B104KO5NNNC</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>100nF 16V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>13133654</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M3" s="2" t="n">
         <v>2</v>
       </c>
@@ -678,88 +746,200 @@
       <c r="P3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>0.0186</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>0.0186</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic 100nF 16V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4,C34</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1nF</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>12pF</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>C1547</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FH (Guangdong Fenghua Advanced Tech)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0402CG120J500NT</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12pF 50V C0G ±5% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>714624</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>0.0144</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0.0144</t>
+        </is>
+      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Basic 12pF 50V C0G ±5% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>C4,C34</t>
+          <t>C6,C8,C29,C31,C32</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>12pF</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>100nF</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>C307331</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CL05B104KB54PNC</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>7934938</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>0.0760</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0.0760</t>
+        </is>
+      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Basic 100nF 16V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
         </is>
       </c>
     </row>
@@ -784,14 +964,40 @@
           <t>C15850</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>CL21A106KAYNNNE</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>3190182</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="M6" s="2" t="n">
         <v>2</v>
       </c>
@@ -804,10 +1010,26 @@
       <c r="P6" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.0767</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1.0738</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>1.0738</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic 10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -830,14 +1052,40 @@
           <t>C15850</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>CL21A106KAYNNNE</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10uF 25V X5R ±10% 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>3190182</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="M7" s="2" t="n">
         <v>2</v>
       </c>
@@ -850,9 +1098,21 @@
       <c r="P7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.0767</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>0.3068</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0.3068</t>
+        </is>
+      </c>
       <c r="T7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
@@ -876,14 +1136,40 @@
           <t>C307331</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CL05B104KB54PNC</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>7934938</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M8" s="2" t="n">
         <v>2</v>
       </c>
@@ -896,9 +1182,21 @@
       <c r="P8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>0.0152</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0.0152</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
@@ -922,14 +1220,40 @@
           <t>C52923</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>CL05A105KA5NQNC</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1uF 25V X5R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>3347699</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M9" s="2" t="n">
         <v>2</v>
       </c>
@@ -942,9 +1266,21 @@
       <c r="P9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.0142</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>0.0284</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0.0284</t>
+        </is>
+      </c>
       <c r="T9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -968,14 +1304,40 @@
           <t>C307331</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>CL05B104KB54PNC</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>7934938</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M10" s="2" t="n">
         <v>2</v>
       </c>
@@ -988,32 +1350,82 @@
       <c r="P10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>0.0152</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0.0152</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic 1uF 25V X5R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>100nF</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>4.7uF</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>C307331</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>CL05B104KB54PNC</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100nF 50V X7R ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>7934938</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M11" s="2" t="n">
         <v>2</v>
       </c>
@@ -1023,117 +1435,207 @@
       <c r="O11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
-        </is>
-      </c>
+      <c r="P11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>0.0152</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0.0152</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C17,C19</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>22u 25V</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_0402_1005Metric</t>
+          <t>Capacitor_SMD:C_1210_3225Metric</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>C307331</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>C52306</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CL32A226KAJNNNE</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>22uF 25V X5R ±10% 1210 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>203557</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.1812</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>0.7248</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0.7248</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended 22uF 25V X5R ±10% 1210 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>C17,C19</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>22u 25V</t>
+          <t>0.5pF</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_1210_3225Metric</t>
+          <t>Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>C52306</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>C778333</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>EYANG(Shenzhen Eyang Tech Development)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>C0402C0G0R6B500NTB</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0.6pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M13" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.0029</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>0.0058</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0.0058</t>
+        </is>
+      </c>
       <c r="T13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>0.5pF</t>
+          <t>0.8pF</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1143,17 +1645,43 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>C778333</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>C3875120</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Venkel</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>C0402C0G500-0R8BNP</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0.8pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>9750</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M14" s="2" t="n">
         <v>2</v>
       </c>
@@ -1166,20 +1694,36 @@
       <c r="P14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.0105</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>0.0210</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0.0210</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended 0.8pF 50V C0G 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C27,C35</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0.8pF</t>
+          <t>12pF</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1189,245 +1733,479 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>C3875120</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>C1547</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>FH (Guangdong Fenghua Advanced Tech)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0402CG120J500NT</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12pF 50V C0G ±5% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>714624</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M15" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>0.0144</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>0.0144</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic 12pF 50V C0G ±5% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C27,C35</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>12pF</t>
+          <t>B3B-PH-K-S</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_0402_1005Metric</t>
+          <t>easyeda2kicad:CONN-TH_B3B-PH-K-S</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>C1547</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>C131339</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>B3B-PH-K-S(LF)(SN)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 100V 1x3P 2A 2mm 3 3P 4.5mm 6mm 7.9mm Brass K Pin PA66 PH Through Hole Tin UL94V-0 White 插件,P=2mm Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Plugin,P=2mm</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>220400</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M16" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.0412</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>0.0824</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0.0824</t>
+        </is>
+      </c>
       <c r="T16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CN1</t>
+          <t>D1,D4,D6,D7,D8,D9,D10,D11</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>B3B-PH-K-S</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-TH_B3B-PH-K-S</t>
+          <t>easyeda2kicad:LED-SMD_L3.0-W3.0_XL-3030UWC-1W-3V</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>C131339</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>C2843891</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>XINGLIGHT</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>XL-3030UWC-1W-3V</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 120° 1W 3.4V 350mA 6500K~7000K Discrete Diode Top-mount White Yellow Lens SMD3030-2P LED Indication - Discrete ROHS</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>SMD3030-2P</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>167784</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="M17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic -40℃~+85℃ 1.8V~2.4V 120° 20mA 300mcd 40mW 615nm~630nm 645nm Discrete Diode Red Water Clear 0603 LED Indication - Discrete ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>D1,D4,D6,D7,D8,D9,D10,D11</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>PRTR5V0U2X</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:LED-SMD_L3.0-W3.0_XL-3030UWC-1W-3V</t>
+          <t>Package_TO_SOT_SMD:SOT-143</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>C2843891</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>C2827688</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>TECH PUBLIC</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>PRTR5V0U2X</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+125℃ 0.3pF、0.8pF 100W 10V、15V 5V 6.5V 6A 80nA ESD IEC 61000-4-2、IEC 61000-4-5、IEC 61000-4-4 Three channels Unidirectional SOT-143 ESD and Surge Protection (TVS/ESD) ROHS</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>SOT-143</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>56619</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0.0609</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>0.1218</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0.1218</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -40℃~+125℃ 140W 1pF 1uA 2 20V 5V 7A 9V ESD IEC 61000-4-2、IEC 61000-4-5 Unidirectional SOT-143 ESD and Surge Protection (TVS/ESD) ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13,D14,D15</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BAV199DW</t>
+          <t>SS34_C8678</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-363_SC-70-6</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>easyeda2kicad:SMA_L4.3-W2.6-LS5.2-RD</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>C8678</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>MDD(Microdiode Semiconductor)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SS34</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+125℃ 3A 40V 500uA@40V 550mV@3A Independent SMA(DO-214AC) Schottky Diodes ROHS</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>SMA(DO-214AC)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>3689172</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="M19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.0301</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>0.1806</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0.1806</t>
+        </is>
+      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Basic -55℃~+125℃ 3A 40V 500uA@40V 550mV@3A Independent SMA(DO-214AC) Schottky Diodes ROHS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SP3012-04UTG</t>
+          <t>XH-2P-SMD</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:UDFN-10_L2.5-W1.0-P0.50-BL</t>
+          <t>easyeda2kicad:CONN-SMD_2P-P2.54_XH2.54-2AB</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>C151304</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>C722696</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>CAX</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2.54-2A-WT</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1x2P 2 2.54mm 2P 500mA 50V 6.1mm 7.8mm Beige LCP Surface Mount, Right Angle Tin XH SMD,P=2.54mm,卧贴 Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=2.54mm,Surface Mount，Right Angle</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1513</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>58</v>
+      </c>
       <c r="M20" s="2" t="n">
         <v>2</v>
       </c>
@@ -1440,40 +2218,82 @@
       <c r="P20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.0455</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>0.0910</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0.0910</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -25℃~+85℃ 1 1x2P 2 2.54mm 2P 500mA 50V 6.1mm 7.8mm Beige LCP Surface Mount, Right Angle Tin XH SMD,P=2.54mm,卧贴 Wire To Board Connector ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>PRTR5V0U2X</t>
+          <t>2.54-3P-LT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-143</t>
+          <t>easyeda2kicad:CONN-SMD_2.54-3P-LT</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>C2827688</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>C722698</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>CAX</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2.54-3P-LT</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1x3P 2.5mm 3 3P 500mA 50V 6mm 7.9mm Beige LCP Phosphor Bronze Surface Mount,Vertical Tin XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=2.5mm</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>46</v>
+      </c>
       <c r="M21" s="2" t="n">
         <v>2</v>
       </c>
@@ -1486,178 +2306,346 @@
       <c r="P21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.0376</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>0.0752</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>0.0752</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -25℃~+85℃ 1 1x3P 2.5mm 3 3P 500mA 50V 6mm 7.9mm Beige LCP Phosphor Bronze Surface Mount,Vertical Tin XH SMD,P=2.5mm Wire To Board Connector ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D13,D14,D15</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SS34_C8678</t>
+          <t>SIM_Card</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:SMA_L4.3-W2.6-LS5.2-RD</t>
+          <t>easyeda2kicad:SIM-SMD_SMN-303</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>C8678</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>C266888</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>XUNPU</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>SMN-303</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1.37mm Connector and Ejector Nano-SIM Card Push-Push With Card Detect SMD SIM Card Connectors ROHS</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>117712</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="M22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.4888</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0.9776</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0.9776</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 117712; Nano-SIM push-push SMD with card detect</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>L2,L3</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>XH-2P-SMD</t>
+          <t>10uH</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_2P-P2.54_XH2.54-2AB</t>
+          <t>easyeda2kicad:IND-SMD_L4.0-W4.0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>C146125</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>C2849472</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>DMBJ</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>PNLS4030-100M 10UH</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10uH 120mΩ 2A 2A Magnetic Shielded Inductor ±20% SMD,4x4mm Power Inductors ROHS</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>SMD,4x4mm</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>10402</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="M23" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
-      <c r="T23" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.052</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>0.208</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0.208</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic 1.85Ω 10uH 17MHz 30@2MHz 3mA ±10% 0603 Inductors (SMD) ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>L4,L5</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2.54-3P-LT</t>
+          <t>2.2uH</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_2.54-3P-LT</t>
+          <t>easyeda2kicad:IND-SMD_L4.0-W4.0_NRS4018T</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>C2681544</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>C92959</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Taiyo Yuden</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NRS4018T2R2MDGJ</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2.2A 2.2uH 3A 42mΩ ±20% SMD,4x4mm Power Inductors ROHS</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>SMD,4x4mm</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>12084</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>3500</v>
+      </c>
       <c r="M24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
-      <c r="T24" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.0884</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>0.3536</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>0.3536</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended 1.2Ω 320mA 520mA 68uH ±20% SMD,4x4mm Power Inductors ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SIM_Card</t>
+          <t>4.7nH</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:SIM-SMD_SMN-303</t>
+          <t>easyeda2kicad:L0402-R-RD</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>C266888</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>C86065</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Murata Electronics</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>LQG15HS4N7S02D</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>160mΩ 4.7nH 6GHz 700mA 8@100MHz Multilayer inductor 0402 Inductors (SMD) ROHS</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>369632</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M25" s="2" t="n">
         <v>2</v>
       </c>
@@ -1670,40 +2658,82 @@
       <c r="P25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr"/>
-      <c r="T25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended 220mA 4.7nH 450mΩ Multilayer inductor 0201 Inductors (SMD) ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>L2,L3</t>
+          <t>LED1,LED2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>10uH</t>
+          <t>19-237/R6GHBHC-A01/2T</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:IND-SMD_L4.0-W4.0</t>
+          <t>easyeda2kicad:LED-ARRAY-SMD_4P-L1.6-W1.6-BL_1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>C2849472</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>C60105</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Everlight Elec</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>19-237/R6GHBHC-A01/2T</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>120° Common Anode SMD-4P,1.6x1.6mm RGB LEDs ROHS</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>SMD-4P,1.6x1.6mm</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>52136</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="M26" s="2" t="n">
         <v>2</v>
       </c>
@@ -1716,86 +2746,166 @@
       <c r="P26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
-      <c r="T26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.0623</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>0.2492</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0.2492</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended 120° Common Anode SMD-4P,1.6x1.6mm RGB LEDs ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>L4,L5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2.2uH</t>
+          <t>PMV20XNER</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:IND-SMD_L4.0-W4.0_NRS4018T</t>
+          <t>easyeda2kicad:SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>C92959</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>C553085</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Nexperia</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>PMV20XNER</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+150℃ 1 N-channel 1.15nF 1.2W 19mΩ@4.5V 30V 650mV 7.2A 85pF SOT-23 MOSFETs ROHS</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>7371</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M27" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.314</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>0.628</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>0.628</t>
+        </is>
+      </c>
       <c r="T27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>4.7nH</t>
+          <t>2N7002</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:L0402-R-RD</t>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>C86065</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t>C8545</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Jiangsu Changjing Electronics Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2N7002</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1 N-channel 115mA 2.5V 225mW 50pF 5pF 5Ω@10V 60V SOT-23 MOSFETs ROHS</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>489975</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M28" s="2" t="n">
         <v>2</v>
       </c>
@@ -1808,82 +2918,170 @@
       <c r="P28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.0153</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>0.0306</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>0.0306</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic 1 N-channel 115mA 2.5V 225mW 50pF 5pF 5Ω@10V 60V SOT-23 MOSFETs ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>LED1,LED2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19-237/R6GHBHC-A01/2T</t>
+          <t>47k</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:LED-ARRAY-SMD_4P-L1.6-W1.6-BL_1</t>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>C60105</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>C25792</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF4702TCE</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 47kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1447799</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr"/>
-      <c r="T29" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic -55℃~+155℃ 47kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>AO3400A</t>
+          <t>330k</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>C22369540</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>HKR(Hong Kong Resistors)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>RCA02150KFLF</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 150kΩ 50V 62.5mW Thick Film Resistor ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M30" s="2" t="n">
         <v>2</v>
       </c>
@@ -1893,71 +3091,123 @@
       <c r="O30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
-        </is>
-      </c>
+      <c r="P30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>0.0008</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0.0008</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>R3,R4,R20,R22</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>C8545</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>C49330233</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>HKR(Hong Kong Resistors)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>AS0210KF</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 10kΩ 50V 62.5mW ±1% ±200ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>5971</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M31" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
+        <v>5971</v>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.0016</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>0.0128</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>9.5536</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic -55℃~+155℃ 10kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R5,R6,R28</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>47k</t>
+          <t>330</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1967,89 +3217,173 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>C25792</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>C25104</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF3300TCE</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 330Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>908691</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M32" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -55℃~+155℃ 33Ω 50V 62.5mW Thick Film Resistor ±100ppm/℃ ±5% 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R7,R8,R9,R10</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>330k</t>
+          <t>39R</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>Resistor_SMD:R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>C22369540</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>C175263</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Ever Ohms Tech</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>CRH2512F39R0E04Z</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 200V 2W 39Ω Thick Film Resistor ±1% ±100ppm/℃ 2512 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2512</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1649</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>4000</v>
+      </c>
       <c r="M33" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.0589</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>0.4712</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>0.4712</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 1649; selected for R7-R10 2W ballast</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>R3,R4,R20,R22</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>150R</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,43 +3393,85 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>C49330233</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>C25082</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF1500TCE</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 150Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>90184</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M34" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>0.0022</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>0.0022</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 90184; 150Ω 1% 0402.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>R5,R6,R28</t>
+          <t>R12,R16,R17</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2105,17 +3481,43 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>C25104</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>C25744</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF1002TCE</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 10kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1894507</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>8956</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M35" s="2" t="n">
         <v>2</v>
       </c>
@@ -2126,80 +3528,172 @@
         <v>6</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr"/>
+        <v>8956</v>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>10.7472</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Basic -55℃~+155℃ 10kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>R7,R8,R9,R10</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>22R</t>
+          <t>560k</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_2512_6332Metric</t>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>C175252</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+          <t>C177266</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>HKR(Hong Kong Resistors)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>RCT02560KJLF</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 50V 560kΩ 62.5mW Thick Film Resistor ±200ppm/℃ ±5% 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>3997</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 3997; 560kΩ 5% 0402.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>150R</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>2.2M</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>C22356219</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>HKR(Hong Kong Resistors)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>RCA022M2JLF</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 2.2MΩ 50V 62.5mW Thick Film Resistor ±200ppm/℃ ±5% 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>12834</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M37" s="2" t="n">
         <v>2</v>
       </c>
@@ -2209,105 +3703,215 @@
       <c r="O37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.0006</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Live-checked: stock 12834; 2.2MΩ 5% 0402.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>R12,R16,R17</t>
+          <t>R15,R29</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>100k</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>C25741</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF1003TCE</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 100kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1333201</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M38" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
-      <c r="S38" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>0.0044</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>11.0000</t>
+        </is>
+      </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Basic -55℃~+155℃ 100kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>R15,R29</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>100k</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>100R</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>C25076</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF1000TCE</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 100Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>3344969</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M39" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Basic -55℃~+155℃ 100Ω 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>100R</t>
+          <t>191k</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2317,17 +3921,43 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>C25076</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t>C159084</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>RALEC</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>RTT021913FTH</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 191kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>9213</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M40" s="2" t="n">
         <v>2</v>
       </c>
@@ -2340,20 +3970,36 @@
       <c r="P40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0.0014</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>0.0014</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -55℃~+155℃ 191kΩ 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>191k</t>
+          <t>240k</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2363,17 +4009,43 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>C159084</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>C64043</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF2403TCE</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 240kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>5286</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M41" s="2" t="n">
         <v>2</v>
       </c>
@@ -2386,20 +4058,36 @@
       <c r="P41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -55℃~+155℃ 240kΩ 50V 62.5mW Thick Film Resistor ±100ppm/℃ ±5% 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>240k</t>
+          <t>18k</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2409,17 +4097,43 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>C64043</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+          <t>C25542</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>0402WGJ0183TCE</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 18kΩ 50V 62.5mW Thick Film Resistor ±100ppm/℃ ±5% 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>15631</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M42" s="2" t="n">
         <v>2</v>
       </c>
@@ -2432,32 +4146,82 @@
       <c r="P42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
-      <c r="T42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0.0014</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>0.0014</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 15631; 18kΩ 5% 0402.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>18k</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+          <t>100k</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>C144809</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>AC0402FR-07100KL</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 100kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M43" s="2" t="n">
         <v>2</v>
       </c>
@@ -2467,85 +4231,173 @@
       <c r="O43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Basic -55℃~+155℃ 100kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R26,R27</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
+          <t>4.7k</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>C25900</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>0402WGF4701TCE</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+155℃ 4.7kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>3849187</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M44" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>0.0044</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>0.0044</t>
+        </is>
+      </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Basic -55℃~+155℃ 4.7kΩ 50V 62.5mW Thick Film Resistor ±1% ±100ppm/℃ 0402 Chip Resistor - Surface Mount ROHS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>Resistor_SMD:R_01005_0402Metric</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>C144809</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t>C364372</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>RC0100JR-070RL</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>-55℃~+125℃ 0Ω 15V 31.25mW Thick Film Resistor ±5% 01005 Chip Resistor - Surface Mount ROHS</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>01005</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>254754</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>20000</v>
+      </c>
       <c r="M45" s="2" t="n">
         <v>2</v>
       </c>
@@ -2558,82 +4410,170 @@
       <c r="P45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
-      <c r="T45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.0026</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>0.0052</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>0.0052</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 254754; 0Ω 01005 jumper resistor.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>R26,R27</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>SW_Push</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0402_1005Metric</t>
+          <t>easyeda2kicad:KEY-SMD_4P-L4.2-W3.2-P2.20-LS4.6</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>C25900</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+          <t>C139797</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ALPSALPINE</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>SKRPACE010</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>-30℃~+85℃ 16V 2.5mm 2.6N 3.2mm 4.2mm 50,000 cycles 50mA J-Lead Oval button SPST-NO Surface Mount,Vertical SMD-4P,4.2x3.2mm Tactile Switches ROHS</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>SMD-4P,4.2x3.2mm</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>127599</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>4000</v>
+      </c>
       <c r="M46" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.0628</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>0.1256</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>0.1256</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -25℃~+85℃ 1.8mm Connector and Ejector MicroSD Card (TF Card) Push-Push SMD SD Card / Memory Card Connector ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>0R</t>
+          <t>nRF52840</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_01005_0402Metric</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
+          <t>Package_DFN_QFN:Nordic_AQFN-73-1EP_7x7mm_P0.5mm</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>C190794</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>NRF52840-QIAA-R</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>-95dBm 1.7V~5.5V 2.4GHz 2.4GHz~2.4835GHz 2Mbps 4.82mA 6.26mA 8dBm SPI、USB、UART、ADC、I2S、PWM ZigBee、Bluetooth、LoRa、ISM transceiver AQFN-73-EP(7x7) RF Transceiver ICs ROHS</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>AQFN-73-EP(7x7)</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>31334</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M47" s="2" t="n">
         <v>2</v>
       </c>
@@ -2643,45 +4583,85 @@
       <c r="O47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>5.7315</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>11.4630</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>11.4630</t>
+        </is>
+      </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Live-checked: stock 31304; AQFN-73-EP(7x7)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SW_Push</t>
+          <t>NRF9151-LACA-R7</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:KEY-SMD_4P-L4.2-W3.2-P2.20-LS4.6</t>
+          <t>easyeda2kicad:LGA-113_L12.1-W11.1_NRF9151-LACA-R7</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>C139797</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+          <t>C22397843</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>nRF9151-LACA-R7</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>LGA-113(12.1x11.1) RF Modules ROHS</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>LGA-113(12.1x11.1)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="M48" s="2" t="n">
         <v>2</v>
       </c>
@@ -2694,80 +4674,170 @@
       <c r="P48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr"/>
-      <c r="S48" s="2" t="inlineStr"/>
-      <c r="T48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>16.1232</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>32.2464</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>32.2464</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended LGA-113(12.1x11.1) RF Modules ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TP1,TP2,TP3</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+          <t>NPM1300</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>easyeda2kicad:BGA-35_L3.1-W2.4-R5-C7-P0.42_NPM1300-CAAA-R</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>C25346894</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Semicon</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>NPM1300-CAAA-R7</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>WLCSP-35(2.4x3.1) Power Management - Specialized ROHS</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>WLCSP-35(2.4x3.1)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="M49" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>2.6665</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>5.3330</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>5.3330</t>
+        </is>
+      </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Extended WLCSP-35(2.4x3.1) Power Management - Specialized ROHS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>nRF52840</t>
+          <t>BMA400</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Package_DFN_QFN:Nordic_AQFN-73-1EP_7x7mm_P0.5mm</t>
+          <t>easyeda2kicad:LGA-12_L2.0-W2.0-P0.50-BL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>C190794</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
+          <t>C437655</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Bosch Sensortec</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>BMA400</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 1.71V~3.6V 12bit 160nA 1KB Accelerometer SPI、I2C X,Y,Z ±16g LGA-12(2x2) Accelerometers ROHS</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>LGA-12(2x2)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>5400</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="M50" s="2" t="n">
         <v>2</v>
       </c>
@@ -2780,40 +4850,82 @@
       <c r="P50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr"/>
-      <c r="S50" s="2" t="inlineStr"/>
-      <c r="T50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>2.3923</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>4.7846</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>4.7846</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -40℃~+85℃ 1.71V~3.6V 12bit 160nA 1KB Accelerometer SPI、I2C X,Y,Z ±16g LGA-12(2x2) Accelerometers ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>NRF9151-LACA-R7</t>
+          <t>DRV8871DDA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:LGA-113_L12.1-W11.1_NRF9151-LACA-R7</t>
+          <t>Package_SO:Texas_HTSOP-8-1EP_3.9x4.9mm_P1.27mm_EP2.95x4.9mm_Mask2.4x3.1mm_ThermalVias</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>C22397843</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
+          <t>C75864</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>DRV8871DDAR</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+125℃ 1 10uA 3.6A 565mΩ PWM Yes SO-8-EP Brushed DC Motor Drivers ROHS</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>SO-8-EP</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>6051</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>2500</v>
+      </c>
       <c r="M51" s="2" t="n">
         <v>2</v>
       </c>
@@ -2826,86 +4938,170 @@
       <c r="P51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr"/>
-      <c r="T51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>2.0294</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>4.0588</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>4.0588</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 6051; SO-8-EP package matches HTSOP-8 exposed-pad footprint.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U6,U10</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>NPM1300</t>
+          <t>BWU.FL-IPEX1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:BGA-35_L3.1-W2.4-R5-C7-P0.42_NPM1300-CAAA-R</t>
+          <t>easyeda2kicad:IPEX-SMD_BWIPX-1-001E</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>C25346894</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
+          <t>C5137195</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>BAT WIRELESS</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>BWU.FL-IPEX1</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1 1.25mm 2mm 50Ω 6GHz Board Side IPEX Male Pin SMD Coaxial Connectors (RF) ROHS</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>708883</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="M52" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr"/>
-      <c r="S52" s="2" t="inlineStr"/>
-      <c r="T52" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.0397</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>0.1588</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>0.1588</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended 1 1.25mm 2mm 50Ω 6GHz Board Side IPEX Male Pin SMD Coaxial Connectors (RF) ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BMA400</t>
+          <t>AN6520-245</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:LGA-12_L2.0-W2.0-P0.50-BL</t>
+          <t>easyeda2kicad:ANT-SMD_L6.5-W2.0</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>C437655</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
+          <t>C239238</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Rainsun microwave Tech</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>AN6520-245</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 0.5dBi 1mm 2 2.2mm 2.45GHz 200MHz 3W 50Ω 6.5mm SMD Antennas ROHS</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="M53" s="2" t="n">
         <v>2</v>
       </c>
@@ -2918,36 +5114,82 @@
       <c r="P53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
-      <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.5727</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>1.1454</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>1.1454</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -40℃~+85℃ 0.5dBi 1mm 2 2.2mm 2.45GHz 200MHz 3W 50Ω 6.5mm SMD Antennas ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>DRV8871DDA</t>
+          <t>SEN0348_CONN</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Package_SO:Texas_HTSOP-8-1EP_3.9x4.9mm_P1.27mm_EP2.95x4.9mm_Mask2.4x3.1mm_ThermalVias</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>easyeda2kicad:CONN-SMD_SM06B-SRSS-TB-LF-SN</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>C160405</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>SM06B-SRSS-TB(LF)(SN)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1A 1mm 1x6P 2.9mm 4.32mm 50V 6 6P 8mm Auxiliary Solder Pin Copper alloy PA SH Surface Mount, Right Angle Tin UL94V-0 White SMD,P=1mm,卧贴 Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=1mm,Surface Mount，Right Angle</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>65256</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M54" s="2" t="n">
         <v>2</v>
       </c>
@@ -2957,183 +5199,349 @@
       <c r="O54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.2994</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>0.5988</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>0.5988</t>
+        </is>
+      </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+          <t>Auto-selected: Extended - Heart Rate Sensors ROHS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>U6,U10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BWU.FL-IPEX1</t>
+          <t>XH-4A</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:IPEX-SMD_BWIPX-1-001E</t>
+          <t>easyeda2kicad:CONN-TH_B4B-XH-A-LF-SN</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>C5137195</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>C2908602</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>HCTL</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>XH-4A</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 1x4P 2.5mm 250V 3A 4 4P 5.9mm 7mm Brass PA66 Through Hole Tin UL94V-0 XH 插件,P=2.5mm Wire To Board Connector ROHS</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Plugin,P=2.5mm</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>181867</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M55" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.0281</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>0.0562</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>0.0562</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 181867; in-stock 4P XH-compatible through-hole connector for B4B-XH footprint.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U11,U14</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>AN6520-245</t>
+          <t>HX PZ1.27-2x5P TP</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:ANT-SMD_L6.5-W2.0</t>
+          <t>easyeda2kicad:HDR-SMD_10P-P1.27-V-M-R2-C5-LS5.5_1</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>C239238</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
+          <t>C41376037</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>hanxia</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>HX PZ1.27-2x5P TP</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+105℃ 1.27mm 1.27mm 10P 1A 1mm 2 2x5P 4mm 500V Black Brass Gold Pin Header Surface Mount,Vertical SMD,P=1.27mm Pin Headers ROHS</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>SMD,P=1.27mm</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>14523</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.0959</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>0.3836</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>0.3836</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 14523; SMD vertical 2x5 1.27mm header, matches HDR-SMD footprint.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U12,U13</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SEN0348_CONN</t>
+          <t>MT3608</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_SM06B-SRSS-TB-LF-SN</t>
+          <t>easyeda2kicad:SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>C160405</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
+          <t>C84817</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>XI'AN Aerosemi Tech</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>MT3608</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>-40℃~+85℃ 1 1.2MHz 100uA、1.6mA 2A 2V~24V Adjustable Boost Boost Built-in No SOT-23-6 DC-DC Converters ROHS</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23-6</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>288847</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M57" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.0799</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>0.3196</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>0.3196</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -40℃~+85℃@(TA) 1 1.2MHz 100uA 2.2V~16V 2.5A Adjustable Boost Boost Built-in No SOT-23-6 DC-DC Converters ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>USB1</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>TYPE-C 16PIN 2MD</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
+          <t>easyeda2kicad:USB-C-SMD_TYPE-C-16PIN-2MD-073</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>C160404</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+          <t>C2765186</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>SHOU HAN</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>TYPE-C 16PIN 2MD(073)</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>-25℃~+85℃ 1 16P 3A 5,000 times 5V Black Female Surface Mount, Right Angle Type-C SMD USB Connectors ROHS</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1378685</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="M58" s="2" t="n">
         <v>2</v>
       </c>
@@ -3146,237 +5554,201 @@
       <c r="P58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q58" s="2" t="inlineStr"/>
-      <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.0736</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>0.1472</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>0.1472</t>
+        </is>
+      </c>
       <c r="T58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>U11,U14</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>HX PZ1.27-2x5P TP</t>
+          <t>32MHz</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:HDR-SMD_10P-P1.27-V-M-R2-C5-LS5.5_1</t>
+          <t>easyeda2kicad:CRYSTAL-SMD_4P-L2.0-W1.6-BL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>C41376037</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
+          <t>C187794</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Seiko Epson</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Q22FA12800025</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>-20℃~+75℃ 32MHz 60Ω 8pF Crystal Oscillator ±10ppm ±10ppm SMD2016-4P Crystals ROHS</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>SMD2016-4P</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>14395</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M59" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr"/>
-      <c r="S59" s="2" t="inlineStr"/>
-      <c r="T59" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.2319</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>0.4638</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>0.4638</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>Auto-selected: Extended -20℃~+70℃ 20pF 32MHz Crystal Oscillator ±20ppm ±20ppm HC-49S-SMD Crystals ROHS</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>U12,U13</t>
+          <t>Y2</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>MT3608</t>
+          <t>32.768kHz</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>easyeda2kicad:SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
+          <t>Crystal:Crystal_SMD_3215-2Pin_3.2x1.5mm</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>C84817</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
+          <t>C70509</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>NDK</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>NX3215SA-32.768KHZ-EXS00A-MU00466</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>32.768kHz Crystal Oscillator ±20ppm SMD3215-2P Crystals ROHS</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>SMD3215-2P</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>3128</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>3000</v>
+      </c>
       <c r="M60" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr"/>
-      <c r="S60" s="2" t="inlineStr"/>
-      <c r="T60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>USB1</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>TYPE-C 16PIN 2MD</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>easyeda2kicad:USB-C-SMD_TYPE-C-16PIN-2MD-073</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>C2765186</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr"/>
-      <c r="S61" s="2" t="inlineStr"/>
-      <c r="T61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>32MHz</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>easyeda2kicad:CRYSTAL-SMD_4P-L2.0-W1.6-BL</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>C187794</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr"/>
-      <c r="S62" s="2" t="inlineStr"/>
-      <c r="T62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>32.768kHz</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P63" s="2" t="inlineStr"/>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr"/>
-      <c r="S63" s="2" t="inlineStr"/>
-      <c r="T63" s="2" t="inlineStr">
-        <is>
-          <t>No LCSC/JLCPCB part selected yet.</t>
+        <v>2</v>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.3009</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>0.6018</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>0.6018</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>Live-checked: stock 3128; 32.768kHz SMD3215-2P crystal.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T63"/>
+  <autoFilter ref="A1:T60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
